--- a/research/traditional_assets/database/data/turkey/turkey_electronics_general.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_electronics_general.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="ibse_manas" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,115 +590,115 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.0443864229765013</v>
+        <v>0.1548317046688382</v>
       </c>
       <c r="H2">
-        <v>-0.1080939947780679</v>
+        <v>0.1296416938110749</v>
       </c>
       <c r="I2">
-        <v>-0.0577023498694517</v>
+        <v>0.08707926167209555</v>
       </c>
       <c r="J2">
-        <v>-0.05133997286419556</v>
+        <v>0.07418381394323198</v>
       </c>
       <c r="K2">
-        <v>0.8149999999999999</v>
+        <v>3.148</v>
       </c>
       <c r="L2">
-        <v>0.2127937336814621</v>
+        <v>0.3418023887079262</v>
       </c>
       <c r="M2">
-        <v>0.056</v>
+        <v>0.144</v>
       </c>
       <c r="N2">
-        <v>0.001414141414141414</v>
+        <v>0.001453077699293643</v>
       </c>
       <c r="O2">
-        <v>0.0687116564417178</v>
+        <v>0.0457433290978399</v>
       </c>
       <c r="P2">
-        <v>0.056</v>
+        <v>0.016</v>
       </c>
       <c r="Q2">
-        <v>0.001414141414141414</v>
+        <v>0.0001614530776992937</v>
       </c>
       <c r="R2">
-        <v>0.0687116564417178</v>
+        <v>0.005082592121982211</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.128</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="U2">
-        <v>4.84</v>
+        <v>3.388</v>
       </c>
       <c r="V2">
-        <v>0.1222222222222222</v>
+        <v>0.03418768920282543</v>
       </c>
       <c r="W2">
-        <v>0.06965811965811966</v>
+        <v>0.1396509461009174</v>
       </c>
       <c r="X2">
-        <v>0.1393311097820666</v>
+        <v>0.2667057435457942</v>
       </c>
       <c r="Y2">
-        <v>-0.06967299012394693</v>
+        <v>-0.1270547974448767</v>
       </c>
       <c r="Z2">
-        <v>1.595833333333333</v>
+        <v>0.4852476290832455</v>
       </c>
       <c r="AA2">
-        <v>-0.08193004002911207</v>
+        <v>0.005554445016602017</v>
       </c>
       <c r="AB2">
-        <v>0.1390311082050999</v>
+        <v>0.2609947135845143</v>
       </c>
       <c r="AC2">
-        <v>-0.220961148234212</v>
+        <v>-0.2554402685679122</v>
       </c>
       <c r="AD2">
-        <v>0.15</v>
+        <v>4.273000000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.15</v>
+        <v>4.273000000000001</v>
       </c>
       <c r="AG2">
-        <v>-4.69</v>
+        <v>0.8850000000000007</v>
       </c>
       <c r="AH2">
-        <v>0.003773584905660377</v>
+        <v>0.04133574531067107</v>
       </c>
       <c r="AI2">
-        <v>0.01357466063348416</v>
+        <v>0.2296941353545127</v>
       </c>
       <c r="AJ2">
-        <v>-0.1343454597536522</v>
+        <v>0.008851327699154881</v>
       </c>
       <c r="AK2">
-        <v>-0.7552334943639289</v>
+        <v>0.05816628327308582</v>
       </c>
       <c r="AL2">
-        <v>0.041</v>
+        <v>0.426</v>
       </c>
       <c r="AM2">
-        <v>-0.396</v>
+        <v>-1.11</v>
       </c>
       <c r="AN2">
-        <v>-0.5905511811023622</v>
+        <v>4.721546961325967</v>
       </c>
       <c r="AO2">
-        <v>-5.390243902439024</v>
+        <v>1.882629107981221</v>
       </c>
       <c r="AP2">
-        <v>18.46456692913386</v>
+        <v>0.9779005524861886</v>
       </c>
       <c r="AQ2">
-        <v>0.5580808080808081</v>
+        <v>-0.7225225225225225</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +709,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Papilon Savunma-Guvenlik Sistemleri Bilisim Muhendislik Hizmetleri Ithalat Ihracat Sanayi ve Ticaret (IBSE:PAPIL)</t>
+          <t>Manas Enerji Yonetimi Sanayi Ve Ticaret Anonim Sirketi (IBSE:MANAS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,115 +718,8952 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.0443864229765013</v>
+        <v>0.2246666666666667</v>
       </c>
       <c r="H3">
-        <v>-0.1080939947780679</v>
+        <v>0.2146666666666667</v>
       </c>
       <c r="I3">
-        <v>-0.0577023498694517</v>
+        <v>0.1653333333333333</v>
       </c>
       <c r="J3">
-        <v>-0.05133997286419556</v>
+        <v>0.1294801498127341</v>
       </c>
       <c r="K3">
-        <v>0.8149999999999999</v>
+        <v>0.698</v>
       </c>
       <c r="L3">
-        <v>0.2127937336814621</v>
+        <v>0.09306666666666666</v>
       </c>
       <c r="M3">
-        <v>0.056</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.001414141414141414</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.0687116564417178</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>0.056</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.001414141414141414</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.0687116564417178</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="U3">
+        <v>0.798</v>
+      </c>
+      <c r="V3">
+        <v>0.01371134020618557</v>
+      </c>
+      <c r="W3">
+        <v>0.05453125</v>
+      </c>
+      <c r="X3">
+        <v>0.2728529462841189</v>
+      </c>
+      <c r="Y3">
+        <v>-0.2183216962841189</v>
+      </c>
+      <c r="Z3">
+        <v>0.5873140172278779</v>
+      </c>
+      <c r="AA3">
+        <v>0.07604550693778431</v>
+      </c>
+      <c r="AB3">
+        <v>0.2615574380421269</v>
+      </c>
+      <c r="AC3">
+        <v>-0.1855119311043426</v>
+      </c>
+      <c r="AD3">
+        <v>4.24</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>4.24</v>
+      </c>
+      <c r="AG3">
+        <v>3.442</v>
+      </c>
+      <c r="AH3">
+        <v>0.06790518898142216</v>
+      </c>
+      <c r="AI3">
+        <v>0.3840579710144928</v>
+      </c>
+      <c r="AJ3">
+        <v>0.05583855163687097</v>
+      </c>
+      <c r="AK3">
+        <v>0.3360671743800039</v>
+      </c>
+      <c r="AL3">
+        <v>0.381</v>
+      </c>
+      <c r="AM3">
+        <v>0.325</v>
+      </c>
+      <c r="AN3">
+        <v>3.212121212121212</v>
+      </c>
+      <c r="AO3">
+        <v>3.254593175853018</v>
+      </c>
+      <c r="AP3">
+        <v>2.607575757575757</v>
+      </c>
+      <c r="AQ3">
+        <v>3.815384615384615</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Papilon Savunma Teknoloji ve Ticaret A.S. (IBSE:PAPIL)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Electronics (General)</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>-0.1514619883040936</v>
+      </c>
+      <c r="H4">
+        <v>-0.2432748538011696</v>
+      </c>
+      <c r="I4">
+        <v>-0.256140350877193</v>
+      </c>
+      <c r="J4">
+        <v>-0.2358224508640021</v>
+      </c>
+      <c r="K4">
+        <v>2.45</v>
+      </c>
+      <c r="L4">
+        <v>1.432748538011696</v>
+      </c>
+      <c r="M4">
+        <v>0.144</v>
+      </c>
+      <c r="N4">
+        <v>0.00352078239608802</v>
+      </c>
+      <c r="O4">
+        <v>0.05877551020408164</v>
+      </c>
+      <c r="P4">
+        <v>0.016</v>
+      </c>
+      <c r="Q4">
+        <v>0.00039119804400978</v>
+      </c>
+      <c r="R4">
+        <v>0.006530612244897959</v>
+      </c>
+      <c r="S4">
+        <v>0.128</v>
+      </c>
+      <c r="T4">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="U4">
+        <v>2.59</v>
+      </c>
+      <c r="V4">
+        <v>0.06332518337408313</v>
+      </c>
+      <c r="W4">
+        <v>0.2247706422018349</v>
+      </c>
+      <c r="X4">
+        <v>0.2605585408074694</v>
+      </c>
+      <c r="Y4">
+        <v>-0.03578789860563455</v>
+      </c>
+      <c r="Z4">
+        <v>0.2753623188405797</v>
+      </c>
+      <c r="AA4">
+        <v>-0.06493661690458027</v>
+      </c>
+      <c r="AB4">
+        <v>0.2604319891269016</v>
+      </c>
+      <c r="AC4">
+        <v>-0.3253686060314819</v>
+      </c>
+      <c r="AD4">
+        <v>0.033</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0.033</v>
+      </c>
+      <c r="AG4">
+        <v>-2.557</v>
+      </c>
+      <c r="AH4">
+        <v>0.0008061954901912883</v>
+      </c>
+      <c r="AI4">
+        <v>0.00436334787782626</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.06668753097045094</v>
+      </c>
+      <c r="AK4">
+        <v>-0.5141765533882967</v>
+      </c>
+      <c r="AL4">
+        <v>0.045</v>
+      </c>
+      <c r="AM4">
+        <v>-1.435</v>
+      </c>
+      <c r="AN4">
+        <v>-0.07951807228915664</v>
+      </c>
+      <c r="AO4">
+        <v>-9.733333333333334</v>
+      </c>
+      <c r="AP4">
+        <v>6.16144578313253</v>
+      </c>
+      <c r="AQ4">
+        <v>0.3052264808362369</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Manas Enerji Yonetimi Sanayi Ve Ticaret Anonim Sirketi (IBSE:MANAS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IBSE:MANAS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Electronics (General)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0679051889814222</v>
+      </c>
+      <c r="F2">
+        <v>0.08</v>
+      </c>
+      <c r="G2">
+        <v>58.2</v>
+      </c>
+      <c r="H2">
+        <v>58.8400363379181</v>
+      </c>
+      <c r="I2">
+        <v>61.642</v>
+      </c>
+      <c r="J2">
+        <v>63.0372363379181</v>
+      </c>
+      <c r="K2">
+        <v>4.24</v>
+      </c>
+      <c r="L2">
+        <v>4.9952</v>
+      </c>
+      <c r="M2">
+        <v>0.261557438042127</v>
+      </c>
+      <c r="N2">
+        <v>0.256627030394941</v>
+      </c>
+      <c r="O2">
+        <v>0.106510603211009</v>
+      </c>
+      <c r="P2">
+        <v>0.04235</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.272852946284119</v>
+      </c>
+      <c r="T2">
+        <v>0.275259815646675</v>
+      </c>
+      <c r="U2">
+        <v>1.36615040191761</v>
+      </c>
+      <c r="V2">
+        <v>1.38019912721341</v>
+      </c>
+      <c r="W2">
+        <v>4.513423795935006</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>58.2</v>
+      </c>
+      <c r="AB2">
+        <v>0.1713229714353474</v>
+      </c>
+      <c r="AC2">
+        <v>0.1383254587155963</v>
+      </c>
+      <c r="AD2">
+        <v>0.23</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>1.32</v>
+      </c>
+      <c r="AH2">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="AI2">
+        <v>1.47</v>
+      </c>
+      <c r="AJ2">
+        <v>4.24</v>
+      </c>
+      <c r="AK2">
+        <v>4.24</v>
+      </c>
+      <c r="AL2">
+        <v>0.381</v>
+      </c>
+      <c r="AM2">
+        <v>4.24</v>
+      </c>
+      <c r="AN2">
+        <v>0.798</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.2604208541105758</v>
+      </c>
+      <c r="C2">
+        <v>62.75613138118182</v>
+      </c>
+      <c r="D2">
+        <v>61.95813138118182</v>
+      </c>
+      <c r="E2">
+        <v>-4.24</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.798</v>
+      </c>
+      <c r="H2">
+        <v>58.2</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1.32</v>
+      </c>
+      <c r="K2">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L2">
+        <v>1.24</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1.24</v>
+      </c>
+      <c r="O2">
+        <v>0.2852</v>
+      </c>
+      <c r="P2">
+        <v>0.9548000000000001</v>
+      </c>
+      <c r="Q2">
+        <v>1.0348</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.2604208541105758</v>
+      </c>
+      <c r="T2">
+        <v>1.293585164054952</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.23</v>
+      </c>
+      <c r="W2">
+        <v>0.035189</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.2598750161461215</v>
+      </c>
+      <c r="C3">
+        <v>62.28470705841593</v>
+      </c>
+      <c r="D3">
+        <v>62.11110705841593</v>
+      </c>
+      <c r="E3">
+        <v>-3.6156</v>
+      </c>
+      <c r="F3">
+        <v>0.6244000000000001</v>
+      </c>
+      <c r="G3">
+        <v>0.798</v>
+      </c>
+      <c r="H3">
+        <v>58.2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1.32</v>
+      </c>
+      <c r="K3">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L3">
+        <v>1.24</v>
+      </c>
+      <c r="M3">
+        <v>0.02853508</v>
+      </c>
+      <c r="N3">
+        <v>1.21146492</v>
+      </c>
+      <c r="O3">
+        <v>0.2786369316</v>
+      </c>
+      <c r="P3">
+        <v>0.9328279884000001</v>
+      </c>
+      <c r="Q3">
+        <v>1.0128279884</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.2621445718647692</v>
+      </c>
       <c r="T3">
-        <v>0</v>
+        <v>1.303646381997602</v>
       </c>
       <c r="U3">
-        <v>4.84</v>
+        <v>0.0457</v>
       </c>
       <c r="V3">
-        <v>0.1222222222222222</v>
+        <v>0.23</v>
       </c>
       <c r="W3">
-        <v>0.06965811965811966</v>
-      </c>
-      <c r="X3">
-        <v>0.1393311097820666</v>
+        <v>0.035189</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
       </c>
       <c r="Y3">
-        <v>-0.06967299012394693</v>
+        <v>43.45528381206571</v>
       </c>
       <c r="Z3">
-        <v>1.595833333333333</v>
-      </c>
-      <c r="AA3">
-        <v>-0.08193004002911207</v>
-      </c>
-      <c r="AB3">
-        <v>0.1390311082050999</v>
-      </c>
-      <c r="AC3">
-        <v>-0.220961148234212</v>
-      </c>
-      <c r="AD3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.2593291781816671</v>
+      </c>
+      <c r="C4">
+        <v>61.81404000444292</v>
+      </c>
+      <c r="D4">
+        <v>62.26484000444292</v>
+      </c>
+      <c r="E4">
+        <v>-2.9912</v>
+      </c>
+      <c r="F4">
+        <v>1.2488</v>
+      </c>
+      <c r="G4">
+        <v>0.798</v>
+      </c>
+      <c r="H4">
+        <v>58.2</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1.32</v>
+      </c>
+      <c r="K4">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L4">
+        <v>1.24</v>
+      </c>
+      <c r="M4">
+        <v>0.05707016000000001</v>
+      </c>
+      <c r="N4">
+        <v>1.18292984</v>
+      </c>
+      <c r="O4">
+        <v>0.2720738631999999</v>
+      </c>
+      <c r="P4">
+        <v>0.9108559768</v>
+      </c>
+      <c r="Q4">
+        <v>0.9908559768</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.2639034675323134</v>
+      </c>
+      <c r="T4">
+        <v>1.313912930918673</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.23</v>
+      </c>
+      <c r="W4">
+        <v>0.035189</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>21.72764190603285</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.2587833402172128</v>
+      </c>
+      <c r="C5">
+        <v>61.34413585622669</v>
+      </c>
+      <c r="D5">
+        <v>62.41933585622669</v>
+      </c>
+      <c r="E5">
+        <v>-2.3668</v>
+      </c>
+      <c r="F5">
+        <v>1.8732</v>
+      </c>
+      <c r="G5">
+        <v>0.798</v>
+      </c>
+      <c r="H5">
+        <v>58.2</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1.32</v>
+      </c>
+      <c r="K5">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L5">
+        <v>1.24</v>
+      </c>
+      <c r="M5">
+        <v>0.08560524000000001</v>
+      </c>
+      <c r="N5">
+        <v>1.15439476</v>
+      </c>
+      <c r="O5">
+        <v>0.2655107947999999</v>
+      </c>
+      <c r="P5">
+        <v>0.8888839652</v>
+      </c>
+      <c r="Q5">
+        <v>0.9688839652000001</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.2656986290899102</v>
+      </c>
+      <c r="T5">
+        <v>1.324391161260797</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.23</v>
+      </c>
+      <c r="W5">
+        <v>0.035189</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>14.4850946040219</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.2582867822527585</v>
+      </c>
+      <c r="C6">
+        <v>60.86095082159834</v>
+      </c>
+      <c r="D6">
+        <v>62.56055082159834</v>
+      </c>
+      <c r="E6">
+        <v>-1.7424</v>
+      </c>
+      <c r="F6">
+        <v>2.4976</v>
+      </c>
+      <c r="G6">
+        <v>0.798</v>
+      </c>
+      <c r="H6">
+        <v>58.2</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1.32</v>
+      </c>
+      <c r="K6">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L6">
+        <v>1.24</v>
+      </c>
+      <c r="M6">
+        <v>0.11813648</v>
+      </c>
+      <c r="N6">
+        <v>1.12186352</v>
+      </c>
+      <c r="O6">
+        <v>0.2580286096</v>
+      </c>
+      <c r="P6">
+        <v>0.8638349104</v>
+      </c>
+      <c r="Q6">
+        <v>0.9438349104000001</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.2675311898466234</v>
+      </c>
+      <c r="T6">
+        <v>1.335087688068382</v>
+      </c>
+      <c r="U6">
+        <v>0.0473</v>
+      </c>
+      <c r="V6">
+        <v>0.23</v>
+      </c>
+      <c r="W6">
+        <v>0.036421</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>10.49633440915118</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.2579727142883042</v>
+      </c>
+      <c r="C7">
+        <v>60.32619822554406</v>
+      </c>
+      <c r="D7">
+        <v>62.65019822554406</v>
+      </c>
+      <c r="E7">
+        <v>-1.118</v>
+      </c>
+      <c r="F7">
+        <v>3.122</v>
+      </c>
+      <c r="G7">
+        <v>0.798</v>
+      </c>
+      <c r="H7">
+        <v>58.2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1.32</v>
+      </c>
+      <c r="K7">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L7">
+        <v>1.24</v>
+      </c>
+      <c r="M7">
+        <v>0.165466</v>
+      </c>
+      <c r="N7">
+        <v>1.074534</v>
+      </c>
+      <c r="O7">
+        <v>0.24714282</v>
+      </c>
+      <c r="P7">
+        <v>0.8273911799999999</v>
+      </c>
+      <c r="Q7">
+        <v>0.90739118</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.2694023308297939</v>
+      </c>
+      <c r="T7">
+        <v>1.346009404914021</v>
+      </c>
+      <c r="U7">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V7">
+        <v>0.23</v>
+      </c>
+      <c r="W7">
+        <v>0.04081000000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>7.493986680043028</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.2574830863238499</v>
+      </c>
+      <c r="C8">
+        <v>59.84207102645195</v>
+      </c>
+      <c r="D8">
+        <v>62.79047102645195</v>
+      </c>
+      <c r="E8">
+        <v>-0.4936000000000003</v>
+      </c>
+      <c r="F8">
+        <v>3.7464</v>
+      </c>
+      <c r="G8">
+        <v>0.798</v>
+      </c>
+      <c r="H8">
+        <v>58.2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1.32</v>
+      </c>
+      <c r="K8">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L8">
+        <v>1.24</v>
+      </c>
+      <c r="M8">
+        <v>0.1985592</v>
+      </c>
+      <c r="N8">
+        <v>1.0414408</v>
+      </c>
+      <c r="O8">
+        <v>0.239531384</v>
+      </c>
+      <c r="P8">
+        <v>0.801909416</v>
+      </c>
+      <c r="Q8">
+        <v>0.8819094160000001</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.2713132833232445</v>
+      </c>
+      <c r="T8">
+        <v>1.357163498713823</v>
+      </c>
+      <c r="U8">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V8">
+        <v>0.23</v>
+      </c>
+      <c r="W8">
+        <v>0.04081000000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>6.244988900035858</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.2571012583593955</v>
+      </c>
+      <c r="C9">
+        <v>59.32749704357776</v>
+      </c>
+      <c r="D9">
+        <v>62.90029704357776</v>
+      </c>
+      <c r="E9">
+        <v>0.1308000000000007</v>
+      </c>
+      <c r="F9">
+        <v>4.370800000000001</v>
+      </c>
+      <c r="G9">
+        <v>0.798</v>
+      </c>
+      <c r="H9">
+        <v>58.2</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1.32</v>
+      </c>
+      <c r="K9">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L9">
+        <v>1.24</v>
+      </c>
+      <c r="M9">
+        <v>0.2403940000000001</v>
+      </c>
+      <c r="N9">
+        <v>0.999606</v>
+      </c>
+      <c r="O9">
+        <v>0.22990938</v>
+      </c>
+      <c r="P9">
+        <v>0.7696966200000001</v>
+      </c>
+      <c r="Q9">
+        <v>0.8496966200000001</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.2732653315692425</v>
+      </c>
+      <c r="T9">
+        <v>1.368557465498567</v>
+      </c>
+      <c r="U9">
+        <v>0.055</v>
+      </c>
+      <c r="V9">
+        <v>0.23</v>
+      </c>
+      <c r="W9">
+        <v>0.04235</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>5.158198623925721</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.2566270303949412</v>
+      </c>
+      <c r="C10">
+        <v>58.84003633791812</v>
+      </c>
+      <c r="D10">
+        <v>63.03723633791812</v>
+      </c>
+      <c r="E10">
+        <v>0.7552000000000003</v>
+      </c>
+      <c r="F10">
+        <v>4.995200000000001</v>
+      </c>
+      <c r="G10">
+        <v>0.798</v>
+      </c>
+      <c r="H10">
+        <v>58.2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1.32</v>
+      </c>
+      <c r="K10">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L10">
+        <v>1.24</v>
+      </c>
+      <c r="M10">
+        <v>0.274736</v>
+      </c>
+      <c r="N10">
+        <v>0.9652639999999999</v>
+      </c>
+      <c r="O10">
+        <v>0.22201072</v>
+      </c>
+      <c r="P10">
+        <v>0.7432532799999999</v>
+      </c>
+      <c r="Q10">
+        <v>0.82325328</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.2752598156466752</v>
+      </c>
+      <c r="T10">
+        <v>1.380199127213414</v>
+      </c>
+      <c r="U10">
+        <v>0.055</v>
+      </c>
+      <c r="V10">
+        <v>0.23</v>
+      </c>
+      <c r="W10">
+        <v>0.04235</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>4.513423795935006</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.2567072024304869</v>
+      </c>
+      <c r="C11">
+        <v>58.19244378853925</v>
+      </c>
+      <c r="D11">
+        <v>63.01404378853925</v>
+      </c>
+      <c r="E11">
+        <v>1.3796</v>
+      </c>
+      <c r="F11">
+        <v>5.6196</v>
+      </c>
+      <c r="G11">
+        <v>0.798</v>
+      </c>
+      <c r="H11">
+        <v>58.2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1.32</v>
+      </c>
+      <c r="K11">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L11">
+        <v>1.24</v>
+      </c>
+      <c r="M11">
+        <v>0.3540348</v>
+      </c>
+      <c r="N11">
+        <v>0.8859652</v>
+      </c>
+      <c r="O11">
+        <v>0.203771996</v>
+      </c>
+      <c r="P11">
+        <v>0.6821932040000001</v>
+      </c>
+      <c r="Q11">
+        <v>0.7621932040000001</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.2772981345389966</v>
+      </c>
+      <c r="T11">
+        <v>1.392096649625291</v>
+      </c>
+      <c r="U11">
+        <v>0.063</v>
+      </c>
+      <c r="V11">
+        <v>0.23</v>
+      </c>
+      <c r="W11">
+        <v>0.04851</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>3.502480547110058</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.2584813744660325</v>
+      </c>
+      <c r="C12">
+        <v>57.05913512658275</v>
+      </c>
+      <c r="D12">
+        <v>62.50513512658274</v>
+      </c>
+      <c r="E12">
+        <v>2.004</v>
+      </c>
+      <c r="F12">
+        <v>6.244000000000001</v>
+      </c>
+      <c r="G12">
+        <v>0.798</v>
+      </c>
+      <c r="H12">
+        <v>58.2</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1.32</v>
+      </c>
+      <c r="K12">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L12">
+        <v>1.24</v>
+      </c>
+      <c r="M12">
+        <v>0.5707016000000001</v>
+      </c>
+      <c r="N12">
+        <v>0.6692983999999998</v>
+      </c>
+      <c r="O12">
+        <v>0.153938632</v>
+      </c>
+      <c r="P12">
+        <v>0.5153597679999999</v>
+      </c>
+      <c r="Q12">
+        <v>0.595359768</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.2793817494067029</v>
+      </c>
+      <c r="T12">
+        <v>1.404258561424098</v>
+      </c>
+      <c r="U12">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V12">
+        <v>0.23</v>
+      </c>
+      <c r="W12">
+        <v>0.07037800000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>2.172764190603285</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.2600745965015783</v>
+      </c>
+      <c r="C13">
+        <v>55.98468545891686</v>
+      </c>
+      <c r="D13">
+        <v>62.05508545891686</v>
+      </c>
+      <c r="E13">
+        <v>2.6284</v>
+      </c>
+      <c r="F13">
+        <v>6.8684</v>
+      </c>
+      <c r="G13">
+        <v>0.798</v>
+      </c>
+      <c r="H13">
+        <v>58.2</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1.32</v>
+      </c>
+      <c r="K13">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L13">
+        <v>1.24</v>
+      </c>
+      <c r="M13">
+        <v>0.772695</v>
+      </c>
+      <c r="N13">
+        <v>0.467305</v>
+      </c>
+      <c r="O13">
+        <v>0.10748015</v>
+      </c>
+      <c r="P13">
+        <v>0.35982485</v>
+      </c>
+      <c r="Q13">
+        <v>0.43982485</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.281512187080425</v>
+      </c>
+      <c r="T13">
+        <v>1.416693774611643</v>
+      </c>
+      <c r="U13">
+        <v>0.1125</v>
+      </c>
+      <c r="V13">
+        <v>0.23</v>
+      </c>
+      <c r="W13">
+        <v>0.08662500000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>1.604772905221336</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.2696403777608417</v>
+      </c>
+      <c r="C14">
+        <v>52.78878830888234</v>
+      </c>
+      <c r="D14">
+        <v>59.48358830888234</v>
+      </c>
+      <c r="E14">
+        <v>3.2528</v>
+      </c>
+      <c r="F14">
+        <v>7.4928</v>
+      </c>
+      <c r="G14">
+        <v>0.798</v>
+      </c>
+      <c r="H14">
+        <v>58.2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>1.32</v>
+      </c>
+      <c r="K14">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L14">
+        <v>1.24</v>
+      </c>
+      <c r="M14">
+        <v>1.47308448</v>
+      </c>
+      <c r="N14">
+        <v>-0.23308448</v>
+      </c>
+      <c r="O14">
+        <v>-0.0536094304</v>
+      </c>
+      <c r="P14">
+        <v>-0.1794750496</v>
+      </c>
+      <c r="Q14">
+        <v>-0.09947504959999998</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.284790866639009</v>
+      </c>
+      <c r="T14">
+        <v>1.435831194019648</v>
+      </c>
+      <c r="U14">
+        <v>0.1966</v>
+      </c>
+      <c r="V14">
+        <v>0.1936073618805623</v>
+      </c>
+      <c r="W14">
+        <v>0.1585367926542814</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.8417711386111406</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.2738686010220852</v>
+      </c>
+      <c r="C15">
+        <v>51.09444578718326</v>
+      </c>
+      <c r="D15">
+        <v>58.41364578718326</v>
+      </c>
+      <c r="E15">
+        <v>3.8772</v>
+      </c>
+      <c r="F15">
+        <v>8.1172</v>
+      </c>
+      <c r="G15">
+        <v>0.798</v>
+      </c>
+      <c r="H15">
+        <v>58.2</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1.32</v>
+      </c>
+      <c r="K15">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L15">
+        <v>1.24</v>
+      </c>
+      <c r="M15">
+        <v>1.73545736</v>
+      </c>
+      <c r="N15">
+        <v>-0.4954573600000001</v>
+      </c>
+      <c r="O15">
+        <v>-0.1139551928</v>
+      </c>
+      <c r="P15">
+        <v>-0.3815021672000001</v>
+      </c>
+      <c r="Q15">
+        <v>-0.3015021672</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.2880944665558292</v>
+      </c>
+      <c r="T15">
+        <v>1.455114071786375</v>
+      </c>
+      <c r="U15">
+        <v>0.2138</v>
+      </c>
+      <c r="V15">
+        <v>0.1643370828771039</v>
+      </c>
+      <c r="W15">
+        <v>0.1786647316808752</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.7145090559874083</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.2756186010220852</v>
+      </c>
+      <c r="C16">
+        <v>50.0383910113912</v>
+      </c>
+      <c r="D16">
+        <v>57.9819910113912</v>
+      </c>
+      <c r="E16">
+        <v>4.501600000000002</v>
+      </c>
+      <c r="F16">
+        <v>8.741600000000002</v>
+      </c>
+      <c r="G16">
+        <v>0.798</v>
+      </c>
+      <c r="H16">
+        <v>58.2</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1.32</v>
+      </c>
+      <c r="K16">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L16">
+        <v>1.24</v>
+      </c>
+      <c r="M16">
+        <v>1.86895408</v>
+      </c>
+      <c r="N16">
+        <v>-0.6289540800000004</v>
+      </c>
+      <c r="O16">
+        <v>-0.1446594384000001</v>
+      </c>
+      <c r="P16">
+        <v>-0.4842946416000004</v>
+      </c>
+      <c r="Q16">
+        <v>-0.4042946416000003</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.2909932394227575</v>
+      </c>
+      <c r="T16">
+        <v>1.472034002853658</v>
+      </c>
+      <c r="U16">
+        <v>0.2138</v>
+      </c>
+      <c r="V16">
+        <v>0.1525987198144536</v>
+      </c>
+      <c r="W16">
+        <v>0.1811743937036698</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.6634726948454506</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
         <v>0.15</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0.15</v>
-      </c>
-      <c r="AG3">
-        <v>-4.69</v>
-      </c>
-      <c r="AH3">
-        <v>0.003773584905660377</v>
-      </c>
-      <c r="AI3">
-        <v>0.01357466063348416</v>
-      </c>
-      <c r="AJ3">
-        <v>-0.1343454597536522</v>
-      </c>
-      <c r="AK3">
-        <v>-0.7552334943639289</v>
-      </c>
-      <c r="AL3">
-        <v>0.041</v>
-      </c>
-      <c r="AM3">
-        <v>-0.396</v>
-      </c>
-      <c r="AN3">
-        <v>-0.5905511811023622</v>
-      </c>
-      <c r="AO3">
-        <v>-5.390243902439024</v>
-      </c>
-      <c r="AP3">
-        <v>18.46456692913386</v>
-      </c>
-      <c r="AQ3">
-        <v>0.5580808080808081</v>
+      <c r="B17">
+        <v>0.2773686010220853</v>
+      </c>
+      <c r="C17">
+        <v>48.98866897053914</v>
+      </c>
+      <c r="D17">
+        <v>57.55666897053914</v>
+      </c>
+      <c r="E17">
+        <v>5.125999999999999</v>
+      </c>
+      <c r="F17">
+        <v>9.366</v>
+      </c>
+      <c r="G17">
+        <v>0.798</v>
+      </c>
+      <c r="H17">
+        <v>58.2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1.32</v>
+      </c>
+      <c r="K17">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L17">
+        <v>1.24</v>
+      </c>
+      <c r="M17">
+        <v>2.0024508</v>
+      </c>
+      <c r="N17">
+        <v>-0.7624507999999997</v>
+      </c>
+      <c r="O17">
+        <v>-0.1753636839999999</v>
+      </c>
+      <c r="P17">
+        <v>-0.5870871159999997</v>
+      </c>
+      <c r="Q17">
+        <v>-0.5070871159999997</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.2939602187100841</v>
+      </c>
+      <c r="T17">
+        <v>1.489352049946055</v>
+      </c>
+      <c r="U17">
+        <v>0.2138</v>
+      </c>
+      <c r="V17">
+        <v>0.1424254718268234</v>
+      </c>
+      <c r="W17">
+        <v>0.1833494341234251</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.6192411818557541</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.2791186010220852</v>
+      </c>
+      <c r="C18">
+        <v>47.94514131970371</v>
+      </c>
+      <c r="D18">
+        <v>57.13754131970371</v>
+      </c>
+      <c r="E18">
+        <v>5.750400000000001</v>
+      </c>
+      <c r="F18">
+        <v>9.990400000000001</v>
+      </c>
+      <c r="G18">
+        <v>0.798</v>
+      </c>
+      <c r="H18">
+        <v>58.2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1.32</v>
+      </c>
+      <c r="K18">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L18">
+        <v>1.24</v>
+      </c>
+      <c r="M18">
+        <v>2.13594752</v>
+      </c>
+      <c r="N18">
+        <v>-0.8959475200000002</v>
+      </c>
+      <c r="O18">
+        <v>-0.2060679296</v>
+      </c>
+      <c r="P18">
+        <v>-0.6898795904000001</v>
+      </c>
+      <c r="Q18">
+        <v>-0.6098795904000001</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.2969978403613946</v>
+      </c>
+      <c r="T18">
+        <v>1.507082431493031</v>
+      </c>
+      <c r="U18">
+        <v>0.2138</v>
+      </c>
+      <c r="V18">
+        <v>0.1335238798376469</v>
+      </c>
+      <c r="W18">
+        <v>0.1852525944907111</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.5805386079897692</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.2808686010220852</v>
+      </c>
+      <c r="C19">
+        <v>46.90767371454017</v>
+      </c>
+      <c r="D19">
+        <v>56.72447371454017</v>
+      </c>
+      <c r="E19">
+        <v>6.374800000000002</v>
+      </c>
+      <c r="F19">
+        <v>10.6148</v>
+      </c>
+      <c r="G19">
+        <v>0.798</v>
+      </c>
+      <c r="H19">
+        <v>58.2</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1.32</v>
+      </c>
+      <c r="K19">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L19">
+        <v>1.24</v>
+      </c>
+      <c r="M19">
+        <v>2.26944424</v>
+      </c>
+      <c r="N19">
+        <v>-1.02944424</v>
+      </c>
+      <c r="O19">
+        <v>-0.2367721752000001</v>
+      </c>
+      <c r="P19">
+        <v>-0.7926720648000003</v>
+      </c>
+      <c r="Q19">
+        <v>-0.7126720648000002</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.3001086577151463</v>
+      </c>
+      <c r="T19">
+        <v>1.525240051149574</v>
+      </c>
+      <c r="U19">
+        <v>0.2138</v>
+      </c>
+      <c r="V19">
+        <v>0.1256695339648441</v>
+      </c>
+      <c r="W19">
+        <v>0.1869318536383163</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.5463892781080182</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.2826186010220852</v>
+      </c>
+      <c r="C20">
+        <v>45.87613566771228</v>
+      </c>
+      <c r="D20">
+        <v>56.31733566771227</v>
+      </c>
+      <c r="E20">
+        <v>6.9992</v>
+      </c>
+      <c r="F20">
+        <v>11.2392</v>
+      </c>
+      <c r="G20">
+        <v>0.798</v>
+      </c>
+      <c r="H20">
+        <v>58.2</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1.32</v>
+      </c>
+      <c r="K20">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L20">
+        <v>1.24</v>
+      </c>
+      <c r="M20">
+        <v>2.40294096</v>
+      </c>
+      <c r="N20">
+        <v>-1.16294096</v>
+      </c>
+      <c r="O20">
+        <v>-0.2674764208</v>
+      </c>
+      <c r="P20">
+        <v>-0.8954645392</v>
+      </c>
+      <c r="Q20">
+        <v>-0.8154645391999999</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.303295348662892</v>
+      </c>
+      <c r="T20">
+        <v>1.543840539578227</v>
+      </c>
+      <c r="U20">
+        <v>0.2138</v>
+      </c>
+      <c r="V20">
+        <v>0.1186878931890195</v>
+      </c>
+      <c r="W20">
+        <v>0.1884245284361876</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.5160343182131283</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.2896142739918303</v>
+      </c>
+      <c r="C21">
+        <v>43.68094124445904</v>
+      </c>
+      <c r="D21">
+        <v>54.74654124445904</v>
+      </c>
+      <c r="E21">
+        <v>7.623600000000001</v>
+      </c>
+      <c r="F21">
+        <v>11.8636</v>
+      </c>
+      <c r="G21">
+        <v>0.798</v>
+      </c>
+      <c r="H21">
+        <v>58.2</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1.32</v>
+      </c>
+      <c r="K21">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L21">
+        <v>1.24</v>
+      </c>
+      <c r="M21">
+        <v>2.833027680000001</v>
+      </c>
+      <c r="N21">
+        <v>-1.593027680000001</v>
+      </c>
+      <c r="O21">
+        <v>-0.3663963664000001</v>
+      </c>
+      <c r="P21">
+        <v>-1.226631313600001</v>
+      </c>
+      <c r="Q21">
+        <v>-1.146631313600001</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.3071726652756993</v>
+      </c>
+      <c r="T21">
+        <v>1.566472160897441</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0.100669683538002</v>
+      </c>
+      <c r="W21">
+        <v>0.2147600795711251</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.4376942762521825</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.2916142739918303</v>
+      </c>
+      <c r="C22">
+        <v>42.62344432805449</v>
+      </c>
+      <c r="D22">
+        <v>54.31344432805449</v>
+      </c>
+      <c r="E22">
+        <v>8.248000000000001</v>
+      </c>
+      <c r="F22">
+        <v>12.488</v>
+      </c>
+      <c r="G22">
+        <v>0.798</v>
+      </c>
+      <c r="H22">
+        <v>58.2</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>1.32</v>
+      </c>
+      <c r="K22">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L22">
+        <v>1.24</v>
+      </c>
+      <c r="M22">
+        <v>2.982134400000001</v>
+      </c>
+      <c r="N22">
+        <v>-1.742134400000001</v>
+      </c>
+      <c r="O22">
+        <v>-0.4006909120000001</v>
+      </c>
+      <c r="P22">
+        <v>-1.341443488</v>
+      </c>
+      <c r="Q22">
+        <v>-1.261443488</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.3105273235916456</v>
+      </c>
+      <c r="T22">
+        <v>1.586053062908659</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0.09563619936110188</v>
+      </c>
+      <c r="W22">
+        <v>0.2159620755925689</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.4158095624395735</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.2936142739918302</v>
+      </c>
+      <c r="C23">
+        <v>41.57274604046488</v>
+      </c>
+      <c r="D23">
+        <v>53.88714604046488</v>
+      </c>
+      <c r="E23">
+        <v>8.872400000000001</v>
+      </c>
+      <c r="F23">
+        <v>13.1124</v>
+      </c>
+      <c r="G23">
+        <v>0.798</v>
+      </c>
+      <c r="H23">
+        <v>58.2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1.32</v>
+      </c>
+      <c r="K23">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L23">
+        <v>1.24</v>
+      </c>
+      <c r="M23">
+        <v>3.13124112</v>
+      </c>
+      <c r="N23">
+        <v>-1.89124112</v>
+      </c>
+      <c r="O23">
+        <v>-0.4349854576000001</v>
+      </c>
+      <c r="P23">
+        <v>-1.4562556624</v>
+      </c>
+      <c r="Q23">
+        <v>-1.3762556624</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.3139669099662233</v>
+      </c>
+      <c r="T23">
+        <v>1.606129683958136</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0.09108209462962083</v>
+      </c>
+      <c r="W23">
+        <v>0.2170495958024466</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.396009107085308</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.2956142739918303</v>
+      </c>
+      <c r="C24">
+        <v>40.52868754405139</v>
+      </c>
+      <c r="D24">
+        <v>53.46748754405139</v>
+      </c>
+      <c r="E24">
+        <v>9.4968</v>
+      </c>
+      <c r="F24">
+        <v>13.7368</v>
+      </c>
+      <c r="G24">
+        <v>0.798</v>
+      </c>
+      <c r="H24">
+        <v>58.2</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1.32</v>
+      </c>
+      <c r="K24">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L24">
+        <v>1.24</v>
+      </c>
+      <c r="M24">
+        <v>3.28034784</v>
+      </c>
+      <c r="N24">
+        <v>-2.04034784</v>
+      </c>
+      <c r="O24">
+        <v>-0.4692800032</v>
+      </c>
+      <c r="P24">
+        <v>-1.5710678368</v>
+      </c>
+      <c r="Q24">
+        <v>-1.4910678368</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.3174946908632262</v>
+      </c>
+      <c r="T24">
+        <v>1.626721090162728</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.08694199941918353</v>
+      </c>
+      <c r="W24">
+        <v>0.218038250538699</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.378008693126885</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.2976142739918303</v>
+      </c>
+      <c r="C25">
+        <v>39.49111491087785</v>
+      </c>
+      <c r="D25">
+        <v>53.05431491087785</v>
+      </c>
+      <c r="E25">
+        <v>10.1212</v>
+      </c>
+      <c r="F25">
+        <v>14.3612</v>
+      </c>
+      <c r="G25">
+        <v>0.798</v>
+      </c>
+      <c r="H25">
+        <v>58.2</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>1.32</v>
+      </c>
+      <c r="K25">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L25">
+        <v>1.24</v>
+      </c>
+      <c r="M25">
+        <v>3.429454560000001</v>
+      </c>
+      <c r="N25">
+        <v>-2.189454560000001</v>
+      </c>
+      <c r="O25">
+        <v>-0.5035745488000001</v>
+      </c>
+      <c r="P25">
+        <v>-1.685880011200001</v>
+      </c>
+      <c r="Q25">
+        <v>-1.6058800112</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.3211141024328785</v>
+      </c>
+      <c r="T25">
+        <v>1.647847338086919</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.08316191248791467</v>
+      </c>
+      <c r="W25">
+        <v>0.218940935297886</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.3615735325561509</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.2996142739918302</v>
+      </c>
+      <c r="C26">
+        <v>38.45987893446547</v>
+      </c>
+      <c r="D26">
+        <v>52.64747893446547</v>
+      </c>
+      <c r="E26">
+        <v>10.7456</v>
+      </c>
+      <c r="F26">
+        <v>14.9856</v>
+      </c>
+      <c r="G26">
+        <v>0.798</v>
+      </c>
+      <c r="H26">
+        <v>58.2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1.32</v>
+      </c>
+      <c r="K26">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L26">
+        <v>1.24</v>
+      </c>
+      <c r="M26">
+        <v>3.57856128</v>
+      </c>
+      <c r="N26">
+        <v>-2.33856128</v>
+      </c>
+      <c r="O26">
+        <v>-0.5378690944000001</v>
+      </c>
+      <c r="P26">
+        <v>-1.8006921856</v>
+      </c>
+      <c r="Q26">
+        <v>-1.7206921856</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.3248287616754164</v>
+      </c>
+      <c r="T26">
+        <v>1.669529539903852</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.07969683280091824</v>
+      </c>
+      <c r="W26">
+        <v>0.2197683963271407</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.3465079686996445</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.3016142739918302</v>
+      </c>
+      <c r="C27">
+        <v>37.43483495014289</v>
+      </c>
+      <c r="D27">
+        <v>52.24683495014289</v>
+      </c>
+      <c r="E27">
+        <v>11.37</v>
+      </c>
+      <c r="F27">
+        <v>15.61</v>
+      </c>
+      <c r="G27">
+        <v>0.798</v>
+      </c>
+      <c r="H27">
+        <v>58.2</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>1.32</v>
+      </c>
+      <c r="K27">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L27">
+        <v>1.24</v>
+      </c>
+      <c r="M27">
+        <v>3.727668</v>
+      </c>
+      <c r="N27">
+        <v>-2.487668</v>
+      </c>
+      <c r="O27">
+        <v>-0.57216364</v>
+      </c>
+      <c r="P27">
+        <v>-1.91550436</v>
+      </c>
+      <c r="Q27">
+        <v>-1.83550436</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.3286424784977552</v>
+      </c>
+      <c r="T27">
+        <v>1.691789933769237</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.07650895948888151</v>
+      </c>
+      <c r="W27">
+        <v>0.2205296604740551</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.3326476499516589</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.3036142739918303</v>
+      </c>
+      <c r="C28">
+        <v>36.41584266353711</v>
+      </c>
+      <c r="D28">
+        <v>51.8522426635371</v>
+      </c>
+      <c r="E28">
+        <v>11.9944</v>
+      </c>
+      <c r="F28">
+        <v>16.2344</v>
+      </c>
+      <c r="G28">
+        <v>0.798</v>
+      </c>
+      <c r="H28">
+        <v>58.2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1.32</v>
+      </c>
+      <c r="K28">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L28">
+        <v>1.24</v>
+      </c>
+      <c r="M28">
+        <v>3.87677472</v>
+      </c>
+      <c r="N28">
+        <v>-2.63677472</v>
+      </c>
+      <c r="O28">
+        <v>-0.6064581856</v>
+      </c>
+      <c r="P28">
+        <v>-2.0303165344</v>
+      </c>
+      <c r="Q28">
+        <v>-1.9503165344</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.332559268747725</v>
+      </c>
+      <c r="T28">
+        <v>1.714651959901253</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.07356630720084761</v>
+      </c>
+      <c r="W28">
+        <v>0.2212323658404376</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.3198535095689027</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.3056142739918303</v>
+      </c>
+      <c r="C29">
+        <v>35.40276598677787</v>
+      </c>
+      <c r="D29">
+        <v>51.46356598677787</v>
+      </c>
+      <c r="E29">
+        <v>12.6188</v>
+      </c>
+      <c r="F29">
+        <v>16.8588</v>
+      </c>
+      <c r="G29">
+        <v>0.798</v>
+      </c>
+      <c r="H29">
+        <v>58.2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1.32</v>
+      </c>
+      <c r="K29">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L29">
+        <v>1.24</v>
+      </c>
+      <c r="M29">
+        <v>4.025881440000001</v>
+      </c>
+      <c r="N29">
+        <v>-2.785881440000001</v>
+      </c>
+      <c r="O29">
+        <v>-0.6407527312000001</v>
+      </c>
+      <c r="P29">
+        <v>-2.145128708800001</v>
+      </c>
+      <c r="Q29">
+        <v>-2.065128708800001</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.3365833683196116</v>
+      </c>
+      <c r="T29">
+        <v>1.738140342913599</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.07084162915637177</v>
+      </c>
+      <c r="W29">
+        <v>0.2218830189574584</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.308007083288573</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.3076142739918302</v>
+      </c>
+      <c r="C30">
+        <v>34.39547288201408</v>
+      </c>
+      <c r="D30">
+        <v>51.08067288201408</v>
+      </c>
+      <c r="E30">
+        <v>13.2432</v>
+      </c>
+      <c r="F30">
+        <v>17.4832</v>
+      </c>
+      <c r="G30">
+        <v>0.798</v>
+      </c>
+      <c r="H30">
+        <v>58.2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1.32</v>
+      </c>
+      <c r="K30">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L30">
+        <v>1.24</v>
+      </c>
+      <c r="M30">
+        <v>4.174988160000001</v>
+      </c>
+      <c r="N30">
+        <v>-2.934988160000001</v>
+      </c>
+      <c r="O30">
+        <v>-0.6750472768000001</v>
+      </c>
+      <c r="P30">
+        <v>-2.259940883200001</v>
+      </c>
+      <c r="Q30">
+        <v>-2.1799408832</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.3407192484351617</v>
+      </c>
+      <c r="T30">
+        <v>1.762281181009621</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.06831157097221563</v>
+      </c>
+      <c r="W30">
+        <v>0.2224871968518349</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.297006830313981</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.3096142739918302</v>
+      </c>
+      <c r="C31">
+        <v>33.39383521186414</v>
+      </c>
+      <c r="D31">
+        <v>50.70343521186414</v>
+      </c>
+      <c r="E31">
+        <v>13.8676</v>
+      </c>
+      <c r="F31">
+        <v>18.1076</v>
+      </c>
+      <c r="G31">
+        <v>0.798</v>
+      </c>
+      <c r="H31">
+        <v>58.2</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1.32</v>
+      </c>
+      <c r="K31">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L31">
+        <v>1.24</v>
+      </c>
+      <c r="M31">
+        <v>4.324094880000001</v>
+      </c>
+      <c r="N31">
+        <v>-3.08409488</v>
+      </c>
+      <c r="O31">
+        <v>-0.7093418224</v>
+      </c>
+      <c r="P31">
+        <v>-2.3747530576</v>
+      </c>
+      <c r="Q31">
+        <v>-2.2947530576</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.3449716322159387</v>
+      </c>
+      <c r="T31">
+        <v>1.787102042713982</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.06595599955938061</v>
+      </c>
+      <c r="W31">
+        <v>0.2230497073052199</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.2867652154755679</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.3116142739918302</v>
+      </c>
+      <c r="C32">
+        <v>32.39772859644428</v>
+      </c>
+      <c r="D32">
+        <v>50.33172859644428</v>
+      </c>
+      <c r="E32">
+        <v>14.492</v>
+      </c>
+      <c r="F32">
+        <v>18.732</v>
+      </c>
+      <c r="G32">
+        <v>0.798</v>
+      </c>
+      <c r="H32">
+        <v>58.2</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1.32</v>
+      </c>
+      <c r="K32">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L32">
+        <v>1.24</v>
+      </c>
+      <c r="M32">
+        <v>4.4732016</v>
+      </c>
+      <c r="N32">
+        <v>-3.2332016</v>
+      </c>
+      <c r="O32">
+        <v>-0.743636368</v>
+      </c>
+      <c r="P32">
+        <v>-2.489565232</v>
+      </c>
+      <c r="Q32">
+        <v>-2.409565232</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.3493455126761664</v>
+      </c>
+      <c r="T32">
+        <v>1.812632071895611</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.06375746624073458</v>
+      </c>
+      <c r="W32">
+        <v>0.2235747170617126</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.2772063749597157</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.3136142739918302</v>
+      </c>
+      <c r="C33">
+        <v>31.40703227664002</v>
+      </c>
+      <c r="D33">
+        <v>49.96543227664002</v>
+      </c>
+      <c r="E33">
+        <v>15.1164</v>
+      </c>
+      <c r="F33">
+        <v>19.3564</v>
+      </c>
+      <c r="G33">
+        <v>0.798</v>
+      </c>
+      <c r="H33">
+        <v>58.2</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1.32</v>
+      </c>
+      <c r="K33">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L33">
+        <v>1.24</v>
+      </c>
+      <c r="M33">
+        <v>4.62230832</v>
+      </c>
+      <c r="N33">
+        <v>-3.38230832</v>
+      </c>
+      <c r="O33">
+        <v>-0.7779309135999999</v>
+      </c>
+      <c r="P33">
+        <v>-2.6043774064</v>
+      </c>
+      <c r="Q33">
+        <v>-2.5243774064</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.3538461722801688</v>
+      </c>
+      <c r="T33">
+        <v>1.838902101923083</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.06170077378135606</v>
+      </c>
+      <c r="W33">
+        <v>0.2240658552210122</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.2682642338319829</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.3156142739918303</v>
+      </c>
+      <c r="C34">
+        <v>30.42162898330467</v>
+      </c>
+      <c r="D34">
+        <v>49.60442898330467</v>
+      </c>
+      <c r="E34">
+        <v>15.7408</v>
+      </c>
+      <c r="F34">
+        <v>19.9808</v>
+      </c>
+      <c r="G34">
+        <v>0.798</v>
+      </c>
+      <c r="H34">
+        <v>58.2</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1.32</v>
+      </c>
+      <c r="K34">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L34">
+        <v>1.24</v>
+      </c>
+      <c r="M34">
+        <v>4.771415040000001</v>
+      </c>
+      <c r="N34">
+        <v>-3.531415040000001</v>
+      </c>
+      <c r="O34">
+        <v>-0.8122254592000001</v>
+      </c>
+      <c r="P34">
+        <v>-2.719189580800001</v>
+      </c>
+      <c r="Q34">
+        <v>-2.639189580800001</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.3584792042254654</v>
+      </c>
+      <c r="T34">
+        <v>1.865944779892541</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.05977262460068867</v>
+      </c>
+      <c r="W34">
+        <v>0.2245262972453556</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.2598809765247334</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.3176142739918302</v>
+      </c>
+      <c r="C35">
+        <v>29.4414048120877</v>
+      </c>
+      <c r="D35">
+        <v>49.2486048120877</v>
+      </c>
+      <c r="E35">
+        <v>16.3652</v>
+      </c>
+      <c r="F35">
+        <v>20.6052</v>
+      </c>
+      <c r="G35">
+        <v>0.798</v>
+      </c>
+      <c r="H35">
+        <v>58.2</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1.32</v>
+      </c>
+      <c r="K35">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L35">
+        <v>1.24</v>
+      </c>
+      <c r="M35">
+        <v>4.920521760000002</v>
+      </c>
+      <c r="N35">
+        <v>-3.680521760000001</v>
+      </c>
+      <c r="O35">
+        <v>-0.8465200048000002</v>
+      </c>
+      <c r="P35">
+        <v>-2.834001755200001</v>
+      </c>
+      <c r="Q35">
+        <v>-2.754001755200001</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.3632505356318156</v>
+      </c>
+      <c r="T35">
+        <v>1.893794701980489</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.05796133294612234</v>
+      </c>
+      <c r="W35">
+        <v>0.224958833692466</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.2520057954179233</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.3196142739918302</v>
+      </c>
+      <c r="C36">
+        <v>28.46624910361169</v>
+      </c>
+      <c r="D36">
+        <v>48.8978491036117</v>
+      </c>
+      <c r="E36">
+        <v>16.9896</v>
+      </c>
+      <c r="F36">
+        <v>21.2296</v>
+      </c>
+      <c r="G36">
+        <v>0.798</v>
+      </c>
+      <c r="H36">
+        <v>58.2</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>1.32</v>
+      </c>
+      <c r="K36">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L36">
+        <v>1.24</v>
+      </c>
+      <c r="M36">
+        <v>5.069628480000001</v>
+      </c>
+      <c r="N36">
+        <v>-3.829628480000001</v>
+      </c>
+      <c r="O36">
+        <v>-0.8808145504000002</v>
+      </c>
+      <c r="P36">
+        <v>-2.948813929600001</v>
+      </c>
+      <c r="Q36">
+        <v>-2.868813929600001</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.3681664528383583</v>
+      </c>
+      <c r="T36">
+        <v>1.922488561101406</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.05625658785947169</v>
+      </c>
+      <c r="W36">
+        <v>0.2253659268191582</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.2445938602585727</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.3216142739918302</v>
+      </c>
+      <c r="C37">
+        <v>27.49605432873394</v>
+      </c>
+      <c r="D37">
+        <v>48.55205432873394</v>
+      </c>
+      <c r="E37">
+        <v>17.614</v>
+      </c>
+      <c r="F37">
+        <v>21.854</v>
+      </c>
+      <c r="G37">
+        <v>0.798</v>
+      </c>
+      <c r="H37">
+        <v>58.2</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1.32</v>
+      </c>
+      <c r="K37">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L37">
+        <v>1.24</v>
+      </c>
+      <c r="M37">
+        <v>5.218735200000001</v>
+      </c>
+      <c r="N37">
+        <v>-3.978735200000001</v>
+      </c>
+      <c r="O37">
+        <v>-0.9151090960000001</v>
+      </c>
+      <c r="P37">
+        <v>-3.063626104000001</v>
+      </c>
+      <c r="Q37">
+        <v>-2.983626104000001</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.3732336290358714</v>
+      </c>
+      <c r="T37">
+        <v>1.952065308195273</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.0546492567777725</v>
+      </c>
+      <c r="W37">
+        <v>0.2257497574814679</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.2376054642511848</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.3236142739918302</v>
+      </c>
+      <c r="C38">
+        <v>26.53071597864179</v>
+      </c>
+      <c r="D38">
+        <v>48.21111597864179</v>
+      </c>
+      <c r="E38">
+        <v>18.2384</v>
+      </c>
+      <c r="F38">
+        <v>22.4784</v>
+      </c>
+      <c r="G38">
+        <v>0.798</v>
+      </c>
+      <c r="H38">
+        <v>58.2</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1.32</v>
+      </c>
+      <c r="K38">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L38">
+        <v>1.24</v>
+      </c>
+      <c r="M38">
+        <v>5.36784192</v>
+      </c>
+      <c r="N38">
+        <v>-4.12784192</v>
+      </c>
+      <c r="O38">
+        <v>-0.9494036415999999</v>
+      </c>
+      <c r="P38">
+        <v>-3.1784382784</v>
+      </c>
+      <c r="Q38">
+        <v>-3.0984382784</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.378459154489557</v>
+      </c>
+      <c r="T38">
+        <v>1.982566328635824</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.05313122186727883</v>
+      </c>
+      <c r="W38">
+        <v>0.2261122642180938</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.2310053124664297</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.3256142739918302</v>
+      </c>
+      <c r="C39">
+        <v>25.57013245954668</v>
+      </c>
+      <c r="D39">
+        <v>47.87493245954668</v>
+      </c>
+      <c r="E39">
+        <v>18.8628</v>
+      </c>
+      <c r="F39">
+        <v>23.1028</v>
+      </c>
+      <c r="G39">
+        <v>0.798</v>
+      </c>
+      <c r="H39">
+        <v>58.2</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1.32</v>
+      </c>
+      <c r="K39">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L39">
+        <v>1.24</v>
+      </c>
+      <c r="M39">
+        <v>5.516948640000001</v>
+      </c>
+      <c r="N39">
+        <v>-4.276948640000001</v>
+      </c>
+      <c r="O39">
+        <v>-0.9836981872</v>
+      </c>
+      <c r="P39">
+        <v>-3.293250452800001</v>
+      </c>
+      <c r="Q39">
+        <v>-3.213250452800001</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.3838505696401848</v>
+      </c>
+      <c r="T39">
+        <v>2.014035635439567</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.05169524289789291</v>
+      </c>
+      <c r="W39">
+        <v>0.2264551759959832</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.2247619256430127</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.3276142739918302</v>
+      </c>
+      <c r="C40">
+        <v>24.6142049917533</v>
+      </c>
+      <c r="D40">
+        <v>47.5434049917533</v>
+      </c>
+      <c r="E40">
+        <v>19.4872</v>
+      </c>
+      <c r="F40">
+        <v>23.7272</v>
+      </c>
+      <c r="G40">
+        <v>0.798</v>
+      </c>
+      <c r="H40">
+        <v>58.2</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>1.32</v>
+      </c>
+      <c r="K40">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L40">
+        <v>1.24</v>
+      </c>
+      <c r="M40">
+        <v>5.666055360000001</v>
+      </c>
+      <c r="N40">
+        <v>-4.426055360000001</v>
+      </c>
+      <c r="O40">
+        <v>-1.0179927328</v>
+      </c>
+      <c r="P40">
+        <v>-3.408062627200001</v>
+      </c>
+      <c r="Q40">
+        <v>-3.328062627200001</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.389415901408575</v>
+      </c>
+      <c r="T40">
+        <v>2.046520081172464</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.05033484176900098</v>
+      </c>
+      <c r="W40">
+        <v>0.2267800397855626</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.2188471381260912</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.3296142739918302</v>
+      </c>
+      <c r="C41">
+        <v>23.66283751289366</v>
+      </c>
+      <c r="D41">
+        <v>47.21643751289366</v>
+      </c>
+      <c r="E41">
+        <v>20.1116</v>
+      </c>
+      <c r="F41">
+        <v>24.3516</v>
+      </c>
+      <c r="G41">
+        <v>0.798</v>
+      </c>
+      <c r="H41">
+        <v>58.2</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>1.32</v>
+      </c>
+      <c r="K41">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L41">
+        <v>1.24</v>
+      </c>
+      <c r="M41">
+        <v>5.81516208</v>
+      </c>
+      <c r="N41">
+        <v>-4.57516208</v>
+      </c>
+      <c r="O41">
+        <v>-1.0522872784</v>
+      </c>
+      <c r="P41">
+        <v>-3.5228748016</v>
+      </c>
+      <c r="Q41">
+        <v>-3.4428748016</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.3951637030710106</v>
+      </c>
+      <c r="T41">
+        <v>2.080069590699881</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.04904420480056507</v>
+      </c>
+      <c r="W41">
+        <v>0.2270882438936251</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.2132356730459352</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.3316142739918302</v>
+      </c>
+      <c r="C42">
+        <v>22.71593658512665</v>
+      </c>
+      <c r="D42">
+        <v>46.89393658512665</v>
+      </c>
+      <c r="E42">
+        <v>20.736</v>
+      </c>
+      <c r="F42">
+        <v>24.976</v>
+      </c>
+      <c r="G42">
+        <v>0.798</v>
+      </c>
+      <c r="H42">
+        <v>58.2</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1.32</v>
+      </c>
+      <c r="K42">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L42">
+        <v>1.24</v>
+      </c>
+      <c r="M42">
+        <v>5.964268800000001</v>
+      </c>
+      <c r="N42">
+        <v>-4.724268800000001</v>
+      </c>
+      <c r="O42">
+        <v>-1.086581824</v>
+      </c>
+      <c r="P42">
+        <v>-3.637686976000001</v>
+      </c>
+      <c r="Q42">
+        <v>-3.557686976000001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.4011030981221941</v>
+      </c>
+      <c r="T42">
+        <v>2.114737417211546</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.04781809968055094</v>
+      </c>
+      <c r="W42">
+        <v>0.2273810377962844</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.2079047812197867</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.3336142739918302</v>
+      </c>
+      <c r="C43">
+        <v>21.77341130611504</v>
+      </c>
+      <c r="D43">
+        <v>46.57581130611504</v>
+      </c>
+      <c r="E43">
+        <v>21.36040000000001</v>
+      </c>
+      <c r="F43">
+        <v>25.6004</v>
+      </c>
+      <c r="G43">
+        <v>0.798</v>
+      </c>
+      <c r="H43">
+        <v>58.2</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>1.32</v>
+      </c>
+      <c r="K43">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L43">
+        <v>1.24</v>
+      </c>
+      <c r="M43">
+        <v>6.113375520000001</v>
+      </c>
+      <c r="N43">
+        <v>-4.873375520000001</v>
+      </c>
+      <c r="O43">
+        <v>-1.1208763696</v>
+      </c>
+      <c r="P43">
+        <v>-3.7524991504</v>
+      </c>
+      <c r="Q43">
+        <v>-3.6724991504</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.4072438285988415</v>
+      </c>
+      <c r="T43">
+        <v>2.150580424282928</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.04665180456639116</v>
+      </c>
+      <c r="W43">
+        <v>0.2276595490695458</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.202833932897353</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.3356142739918302</v>
+      </c>
+      <c r="C44">
+        <v>20.83517322360156</v>
+      </c>
+      <c r="D44">
+        <v>46.26197322360157</v>
+      </c>
+      <c r="E44">
+        <v>21.9848</v>
+      </c>
+      <c r="F44">
+        <v>26.2248</v>
+      </c>
+      <c r="G44">
+        <v>0.798</v>
+      </c>
+      <c r="H44">
+        <v>58.2</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>1.32</v>
+      </c>
+      <c r="K44">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L44">
+        <v>1.24</v>
+      </c>
+      <c r="M44">
+        <v>6.262482240000001</v>
+      </c>
+      <c r="N44">
+        <v>-5.02248224</v>
+      </c>
+      <c r="O44">
+        <v>-1.1551709152</v>
+      </c>
+      <c r="P44">
+        <v>-3.8673113248</v>
+      </c>
+      <c r="Q44">
+        <v>-3.7873113248</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.4135963084022697</v>
+      </c>
+      <c r="T44">
+        <v>2.187659397115392</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.04554104731481042</v>
+      </c>
+      <c r="W44">
+        <v>0.2279247979012233</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.198004553542654</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.3376142739918302</v>
+      </c>
+      <c r="C45">
+        <v>19.90113625341542</v>
+      </c>
+      <c r="D45">
+        <v>45.95233625341542</v>
+      </c>
+      <c r="E45">
+        <v>22.6092</v>
+      </c>
+      <c r="F45">
+        <v>26.8492</v>
+      </c>
+      <c r="G45">
+        <v>0.798</v>
+      </c>
+      <c r="H45">
+        <v>58.2</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>1.32</v>
+      </c>
+      <c r="K45">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L45">
+        <v>1.24</v>
+      </c>
+      <c r="M45">
+        <v>6.411588960000001</v>
+      </c>
+      <c r="N45">
+        <v>-5.171588960000001</v>
+      </c>
+      <c r="O45">
+        <v>-1.1894654608</v>
+      </c>
+      <c r="P45">
+        <v>-3.982123499200001</v>
+      </c>
+      <c r="Q45">
+        <v>-3.902123499200001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.4201716822338885</v>
+      </c>
+      <c r="T45">
+        <v>2.226039386538469</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.04448195319121018</v>
+      </c>
+      <c r="W45">
+        <v>0.228177709577939</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.1933997964835226</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.3396142739918303</v>
+      </c>
+      <c r="C46">
+        <v>18.97121660074983</v>
+      </c>
+      <c r="D46">
+        <v>45.64681660074983</v>
+      </c>
+      <c r="E46">
+        <v>23.2336</v>
+      </c>
+      <c r="F46">
+        <v>27.4736</v>
+      </c>
+      <c r="G46">
+        <v>0.798</v>
+      </c>
+      <c r="H46">
+        <v>58.2</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>1.32</v>
+      </c>
+      <c r="K46">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L46">
+        <v>1.24</v>
+      </c>
+      <c r="M46">
+        <v>6.56069568</v>
+      </c>
+      <c r="N46">
+        <v>-5.32069568</v>
+      </c>
+      <c r="O46">
+        <v>-1.2237600064</v>
+      </c>
+      <c r="P46">
+        <v>-4.0969356736</v>
+      </c>
+      <c r="Q46">
+        <v>-4.0169356736</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.4269818908452079</v>
+      </c>
+      <c r="T46">
+        <v>2.265790089869513</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.04347099970959176</v>
+      </c>
+      <c r="W46">
+        <v>0.2284191252693495</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.1890043465634426</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.3416142739918302</v>
+      </c>
+      <c r="C47">
+        <v>18.04533268455914</v>
+      </c>
+      <c r="D47">
+        <v>45.34533268455914</v>
+      </c>
+      <c r="E47">
+        <v>23.858</v>
+      </c>
+      <c r="F47">
+        <v>28.098</v>
+      </c>
+      <c r="G47">
+        <v>0.798</v>
+      </c>
+      <c r="H47">
+        <v>58.2</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1.32</v>
+      </c>
+      <c r="K47">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L47">
+        <v>1.24</v>
+      </c>
+      <c r="M47">
+        <v>6.709802400000001</v>
+      </c>
+      <c r="N47">
+        <v>-5.469802400000001</v>
+      </c>
+      <c r="O47">
+        <v>-1.258054552</v>
+      </c>
+      <c r="P47">
+        <v>-4.211747848000001</v>
+      </c>
+      <c r="Q47">
+        <v>-4.131747848000001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.4340397434060299</v>
+      </c>
+      <c r="T47">
+        <v>2.306986273321686</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.04250497749382306</v>
+      </c>
+      <c r="W47">
+        <v>0.2286498113744751</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.1848042499731438</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.3436142739918303</v>
+      </c>
+      <c r="C48">
+        <v>17.12340506493215</v>
+      </c>
+      <c r="D48">
+        <v>45.04780506493215</v>
+      </c>
+      <c r="E48">
+        <v>24.48240000000001</v>
+      </c>
+      <c r="F48">
+        <v>28.7224</v>
+      </c>
+      <c r="G48">
+        <v>0.798</v>
+      </c>
+      <c r="H48">
+        <v>58.2</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>1.32</v>
+      </c>
+      <c r="K48">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L48">
+        <v>1.24</v>
+      </c>
+      <c r="M48">
+        <v>6.858909120000002</v>
+      </c>
+      <c r="N48">
+        <v>-5.618909120000001</v>
+      </c>
+      <c r="O48">
+        <v>-1.2923490976</v>
+      </c>
+      <c r="P48">
+        <v>-4.326560022400001</v>
+      </c>
+      <c r="Q48">
+        <v>-4.246560022400001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.441358997913549</v>
+      </c>
+      <c r="T48">
+        <v>2.349708241346162</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.04158095624395734</v>
+      </c>
+      <c r="W48">
+        <v>0.228870467648943</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.1807867662780754</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.3456142739918303</v>
+      </c>
+      <c r="C49">
+        <v>16.2053563733062</v>
+      </c>
+      <c r="D49">
+        <v>44.7541563733062</v>
+      </c>
+      <c r="E49">
+        <v>25.10680000000001</v>
+      </c>
+      <c r="F49">
+        <v>29.34680000000001</v>
+      </c>
+      <c r="G49">
+        <v>0.798</v>
+      </c>
+      <c r="H49">
+        <v>58.2</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1.32</v>
+      </c>
+      <c r="K49">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L49">
+        <v>1.24</v>
+      </c>
+      <c r="M49">
+        <v>7.008015840000001</v>
+      </c>
+      <c r="N49">
+        <v>-5.768015840000001</v>
+      </c>
+      <c r="O49">
+        <v>-1.3266436432</v>
+      </c>
+      <c r="P49">
+        <v>-4.441372196800002</v>
+      </c>
+      <c r="Q49">
+        <v>-4.361372196800001</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.4489544507043707</v>
+      </c>
+      <c r="T49">
+        <v>2.39404235910741</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.04069625504727739</v>
+      </c>
+      <c r="W49">
+        <v>0.2290817342947102</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.1769402393359887</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.3476142739918302</v>
+      </c>
+      <c r="C50">
+        <v>15.29111124539293</v>
+      </c>
+      <c r="D50">
+        <v>44.46431124539293</v>
+      </c>
+      <c r="E50">
+        <v>25.7312</v>
+      </c>
+      <c r="F50">
+        <v>29.9712</v>
+      </c>
+      <c r="G50">
+        <v>0.798</v>
+      </c>
+      <c r="H50">
+        <v>58.2</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>1.32</v>
+      </c>
+      <c r="K50">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L50">
+        <v>1.24</v>
+      </c>
+      <c r="M50">
+        <v>7.15712256</v>
+      </c>
+      <c r="N50">
+        <v>-5.91712256</v>
+      </c>
+      <c r="O50">
+        <v>-1.3609381888</v>
+      </c>
+      <c r="P50">
+        <v>-4.556184371200001</v>
+      </c>
+      <c r="Q50">
+        <v>-4.4761843712</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.4568420362948393</v>
+      </c>
+      <c r="T50">
+        <v>2.440081635244091</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.03984841640045912</v>
+      </c>
+      <c r="W50">
+        <v>0.2292841981635704</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.1732539843498223</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.3496142739918303</v>
+      </c>
+      <c r="C51">
+        <v>14.3805962566935</v>
+      </c>
+      <c r="D51">
+        <v>44.1781962566935</v>
+      </c>
+      <c r="E51">
+        <v>26.3556</v>
+      </c>
+      <c r="F51">
+        <v>30.5956</v>
+      </c>
+      <c r="G51">
+        <v>0.798</v>
+      </c>
+      <c r="H51">
+        <v>58.2</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>1.32</v>
+      </c>
+      <c r="K51">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L51">
+        <v>1.24</v>
+      </c>
+      <c r="M51">
+        <v>7.306229280000001</v>
+      </c>
+      <c r="N51">
+        <v>-6.066229280000001</v>
+      </c>
+      <c r="O51">
+        <v>-1.3952327344</v>
+      </c>
+      <c r="P51">
+        <v>-4.6709965456</v>
+      </c>
+      <c r="Q51">
+        <v>-4.5909965456</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.4650389389672872</v>
+      </c>
+      <c r="T51">
+        <v>2.487926373190054</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.03903518341269464</v>
+      </c>
+      <c r="W51">
+        <v>0.2294783982010485</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.1697181887508463</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.3516142739918302</v>
+      </c>
+      <c r="C52">
+        <v>13.47373986048797</v>
+      </c>
+      <c r="D52">
+        <v>43.89573986048797</v>
+      </c>
+      <c r="E52">
+        <v>26.98</v>
+      </c>
+      <c r="F52">
+        <v>31.22</v>
+      </c>
+      <c r="G52">
+        <v>0.798</v>
+      </c>
+      <c r="H52">
+        <v>58.2</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>1.32</v>
+      </c>
+      <c r="K52">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L52">
+        <v>1.24</v>
+      </c>
+      <c r="M52">
+        <v>7.455336000000001</v>
+      </c>
+      <c r="N52">
+        <v>-6.215336000000001</v>
+      </c>
+      <c r="O52">
+        <v>-1.42952728</v>
+      </c>
+      <c r="P52">
+        <v>-4.78580872</v>
+      </c>
+      <c r="Q52">
+        <v>-4.70580872</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.4735637177466329</v>
+      </c>
+      <c r="T52">
+        <v>2.537684900653855</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.03825447974444075</v>
+      </c>
+      <c r="W52">
+        <v>0.2296648302370276</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.1663238249758294</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.3536142739918303</v>
+      </c>
+      <c r="C53">
+        <v>12.57047232818777</v>
+      </c>
+      <c r="D53">
+        <v>43.61687232818777</v>
+      </c>
+      <c r="E53">
+        <v>27.60440000000001</v>
+      </c>
+      <c r="F53">
+        <v>31.8444</v>
+      </c>
+      <c r="G53">
+        <v>0.798</v>
+      </c>
+      <c r="H53">
+        <v>58.2</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>1.32</v>
+      </c>
+      <c r="K53">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L53">
+        <v>1.24</v>
+      </c>
+      <c r="M53">
+        <v>7.604442720000002</v>
+      </c>
+      <c r="N53">
+        <v>-6.364442720000001</v>
+      </c>
+      <c r="O53">
+        <v>-1.4638218256</v>
+      </c>
+      <c r="P53">
+        <v>-4.900620894400001</v>
+      </c>
+      <c r="Q53">
+        <v>-4.820620894400001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.4824364466802377</v>
+      </c>
+      <c r="T53">
+        <v>2.589474388422301</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.03750439190631447</v>
+      </c>
+      <c r="W53">
+        <v>0.2298439512127721</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.1630625735057151</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.3556142739918302</v>
+      </c>
+      <c r="C54">
+        <v>11.67072569194808</v>
+      </c>
+      <c r="D54">
+        <v>43.34152569194808</v>
+      </c>
+      <c r="E54">
+        <v>28.2288</v>
+      </c>
+      <c r="F54">
+        <v>32.4688</v>
+      </c>
+      <c r="G54">
+        <v>0.798</v>
+      </c>
+      <c r="H54">
+        <v>58.2</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>1.32</v>
+      </c>
+      <c r="K54">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L54">
+        <v>1.24</v>
+      </c>
+      <c r="M54">
+        <v>7.75354944</v>
+      </c>
+      <c r="N54">
+        <v>-6.51354944</v>
+      </c>
+      <c r="O54">
+        <v>-1.4981163712</v>
+      </c>
+      <c r="P54">
+        <v>-5.0154330688</v>
+      </c>
+      <c r="Q54">
+        <v>-4.9354330688</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.4916788726527426</v>
+      </c>
+      <c r="T54">
+        <v>2.643421771514432</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.03678315360042381</v>
+      </c>
+      <c r="W54">
+        <v>0.2300161829202188</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.1599267547844514</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.3576142739918302</v>
+      </c>
+      <c r="C55">
+        <v>10.77443368943969</v>
+      </c>
+      <c r="D55">
+        <v>43.06963368943969</v>
+      </c>
+      <c r="E55">
+        <v>28.8532</v>
+      </c>
+      <c r="F55">
+        <v>33.0932</v>
+      </c>
+      <c r="G55">
+        <v>0.798</v>
+      </c>
+      <c r="H55">
+        <v>58.2</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1.32</v>
+      </c>
+      <c r="K55">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L55">
+        <v>1.24</v>
+      </c>
+      <c r="M55">
+        <v>7.902656160000001</v>
+      </c>
+      <c r="N55">
+        <v>-6.662656160000001</v>
+      </c>
+      <c r="O55">
+        <v>-1.5324109168</v>
+      </c>
+      <c r="P55">
+        <v>-5.130245243200001</v>
+      </c>
+      <c r="Q55">
+        <v>-5.050245243200001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.5013145933474819</v>
+      </c>
+      <c r="T55">
+        <v>2.699664787929633</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.03608913183437807</v>
+      </c>
+      <c r="W55">
+        <v>0.2301819153179505</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.156909268845122</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.3596142739918302</v>
+      </c>
+      <c r="C56">
+        <v>9.881531710687106</v>
+      </c>
+      <c r="D56">
+        <v>42.80113171068711</v>
+      </c>
+      <c r="E56">
+        <v>29.4776</v>
+      </c>
+      <c r="F56">
+        <v>33.7176</v>
+      </c>
+      <c r="G56">
+        <v>0.798</v>
+      </c>
+      <c r="H56">
+        <v>58.2</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>1.32</v>
+      </c>
+      <c r="K56">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L56">
+        <v>1.24</v>
+      </c>
+      <c r="M56">
+        <v>8.051762880000002</v>
+      </c>
+      <c r="N56">
+        <v>-6.811762880000002</v>
+      </c>
+      <c r="O56">
+        <v>-1.5667054624</v>
+      </c>
+      <c r="P56">
+        <v>-5.245057417600002</v>
+      </c>
+      <c r="Q56">
+        <v>-5.165057417600002</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.5113692584202532</v>
+      </c>
+      <c r="T56">
+        <v>2.758353152884625</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.03542081457818588</v>
+      </c>
+      <c r="W56">
+        <v>0.2303415094787292</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.1540035416442864</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.3616142739918302</v>
+      </c>
+      <c r="C57">
+        <v>8.991956746882558</v>
+      </c>
+      <c r="D57">
+        <v>42.53595674688256</v>
+      </c>
+      <c r="E57">
+        <v>30.102</v>
+      </c>
+      <c r="F57">
+        <v>34.34200000000001</v>
+      </c>
+      <c r="G57">
+        <v>0.798</v>
+      </c>
+      <c r="H57">
+        <v>58.2</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>1.32</v>
+      </c>
+      <c r="K57">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L57">
+        <v>1.24</v>
+      </c>
+      <c r="M57">
+        <v>8.200869600000003</v>
+      </c>
+      <c r="N57">
+        <v>-6.960869600000002</v>
+      </c>
+      <c r="O57">
+        <v>-1.601000008</v>
+      </c>
+      <c r="P57">
+        <v>-5.359869592000002</v>
+      </c>
+      <c r="Q57">
+        <v>-5.279869592000002</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.5218707974962589</v>
+      </c>
+      <c r="T57">
+        <v>2.819649889615395</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.03477679976767341</v>
+      </c>
+      <c r="W57">
+        <v>0.2304953002154796</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.151203477250754</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.3636142739918302</v>
+      </c>
+      <c r="C58">
+        <v>8.105647341091156</v>
+      </c>
+      <c r="D58">
+        <v>42.27404734109116</v>
+      </c>
+      <c r="E58">
+        <v>30.72640000000001</v>
+      </c>
+      <c r="F58">
+        <v>34.96640000000001</v>
+      </c>
+      <c r="G58">
+        <v>0.798</v>
+      </c>
+      <c r="H58">
+        <v>58.2</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>1.32</v>
+      </c>
+      <c r="K58">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L58">
+        <v>1.24</v>
+      </c>
+      <c r="M58">
+        <v>8.349976320000001</v>
+      </c>
+      <c r="N58">
+        <v>-7.109976320000001</v>
+      </c>
+      <c r="O58">
+        <v>-1.6352945536</v>
+      </c>
+      <c r="P58">
+        <v>-5.474681766400002</v>
+      </c>
+      <c r="Q58">
+        <v>-5.394681766400002</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.5328496792575373</v>
+      </c>
+      <c r="T58">
+        <v>2.883732841652108</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.03415578548610781</v>
+      </c>
+      <c r="W58">
+        <v>0.2306435984259174</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.1485034151569905</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.3656142739918302</v>
+      </c>
+      <c r="C59">
+        <v>7.222543540766033</v>
+      </c>
+      <c r="D59">
+        <v>42.01534354076604</v>
+      </c>
+      <c r="E59">
+        <v>31.35080000000001</v>
+      </c>
+      <c r="F59">
+        <v>35.59080000000001</v>
+      </c>
+      <c r="G59">
+        <v>0.798</v>
+      </c>
+      <c r="H59">
+        <v>58.2</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>1.32</v>
+      </c>
+      <c r="K59">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L59">
+        <v>1.24</v>
+      </c>
+      <c r="M59">
+        <v>8.499083040000002</v>
+      </c>
+      <c r="N59">
+        <v>-7.259083040000002</v>
+      </c>
+      <c r="O59">
+        <v>-1.6695890992</v>
+      </c>
+      <c r="P59">
+        <v>-5.589493940800002</v>
+      </c>
+      <c r="Q59">
+        <v>-5.509493940800001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.5443392066821313</v>
+      </c>
+      <c r="T59">
+        <v>2.950796396109134</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.03355656117933398</v>
+      </c>
+      <c r="W59">
+        <v>0.230786693190375</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.1458980920840609</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.3676142739918302</v>
+      </c>
+      <c r="C60">
+        <v>6.342586851996437</v>
+      </c>
+      <c r="D60">
+        <v>41.75978685199644</v>
+      </c>
+      <c r="E60">
+        <v>31.9752</v>
+      </c>
+      <c r="F60">
+        <v>36.2152</v>
+      </c>
+      <c r="G60">
+        <v>0.798</v>
+      </c>
+      <c r="H60">
+        <v>58.2</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>1.32</v>
+      </c>
+      <c r="K60">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L60">
+        <v>1.24</v>
+      </c>
+      <c r="M60">
+        <v>8.648189760000001</v>
+      </c>
+      <c r="N60">
+        <v>-7.408189760000001</v>
+      </c>
+      <c r="O60">
+        <v>-1.7038836448</v>
+      </c>
+      <c r="P60">
+        <v>-5.704306115200001</v>
+      </c>
+      <c r="Q60">
+        <v>-5.6243061152</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.5563758544602773</v>
+      </c>
+      <c r="T60">
+        <v>3.021053453159351</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.03297799977969031</v>
+      </c>
+      <c r="W60">
+        <v>0.23092485365261</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.143382607737784</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.3696142739918302</v>
+      </c>
+      <c r="C61">
+        <v>5.465720195415429</v>
+      </c>
+      <c r="D61">
+        <v>41.50732019541543</v>
+      </c>
+      <c r="E61">
+        <v>32.5996</v>
+      </c>
+      <c r="F61">
+        <v>36.8396</v>
+      </c>
+      <c r="G61">
+        <v>0.798</v>
+      </c>
+      <c r="H61">
+        <v>58.2</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>1.32</v>
+      </c>
+      <c r="K61">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L61">
+        <v>1.24</v>
+      </c>
+      <c r="M61">
+        <v>8.797296480000002</v>
+      </c>
+      <c r="N61">
+        <v>-7.557296480000002</v>
+      </c>
+      <c r="O61">
+        <v>-1.7381781904</v>
+      </c>
+      <c r="P61">
+        <v>-5.819118289600001</v>
+      </c>
+      <c r="Q61">
+        <v>-5.739118289600001</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.5689996557885766</v>
+      </c>
+      <c r="T61">
+        <v>3.094737683724213</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.03241905063088199</v>
+      </c>
+      <c r="W61">
+        <v>0.2310583307093454</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.1409523940473131</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.3716142739918302</v>
+      </c>
+      <c r="C62">
+        <v>4.591887863697387</v>
+      </c>
+      <c r="D62">
+        <v>41.25788786369738</v>
+      </c>
+      <c r="E62">
+        <v>33.224</v>
+      </c>
+      <c r="F62">
+        <v>37.464</v>
+      </c>
+      <c r="G62">
+        <v>0.798</v>
+      </c>
+      <c r="H62">
+        <v>58.2</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1.32</v>
+      </c>
+      <c r="K62">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L62">
+        <v>1.24</v>
+      </c>
+      <c r="M62">
+        <v>8.946403200000001</v>
+      </c>
+      <c r="N62">
+        <v>-7.7064032</v>
+      </c>
+      <c r="O62">
+        <v>-1.772472736</v>
+      </c>
+      <c r="P62">
+        <v>-5.933930464</v>
+      </c>
+      <c r="Q62">
+        <v>-5.853930464</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.582254647183291</v>
+      </c>
+      <c r="T62">
+        <v>3.172106125817318</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.03187873312036729</v>
+      </c>
+      <c r="W62">
+        <v>0.2311873585308563</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.1386031874798579</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.3736142739918303</v>
+      </c>
+      <c r="C63">
+        <v>3.72103548057882</v>
+      </c>
+      <c r="D63">
+        <v>41.01143548057882</v>
+      </c>
+      <c r="E63">
+        <v>33.8484</v>
+      </c>
+      <c r="F63">
+        <v>38.0884</v>
+      </c>
+      <c r="G63">
+        <v>0.798</v>
+      </c>
+      <c r="H63">
+        <v>58.2</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>1.32</v>
+      </c>
+      <c r="K63">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L63">
+        <v>1.24</v>
+      </c>
+      <c r="M63">
+        <v>9.095509920000001</v>
+      </c>
+      <c r="N63">
+        <v>-7.855509920000001</v>
+      </c>
+      <c r="O63">
+        <v>-1.8067672816</v>
+      </c>
+      <c r="P63">
+        <v>-6.048742638400001</v>
+      </c>
+      <c r="Q63">
+        <v>-5.968742638400001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.5961893817264525</v>
+      </c>
+      <c r="T63">
+        <v>3.253442180325455</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.03135613093806619</v>
+      </c>
+      <c r="W63">
+        <v>0.2313121559319898</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.1363310040785487</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.3756142739918302</v>
+      </c>
+      <c r="C64">
+        <v>2.853109961339257</v>
+      </c>
+      <c r="D64">
+        <v>40.76790996133926</v>
+      </c>
+      <c r="E64">
+        <v>34.4728</v>
+      </c>
+      <c r="F64">
+        <v>38.7128</v>
+      </c>
+      <c r="G64">
+        <v>0.798</v>
+      </c>
+      <c r="H64">
+        <v>58.2</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>1.32</v>
+      </c>
+      <c r="K64">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L64">
+        <v>1.24</v>
+      </c>
+      <c r="M64">
+        <v>9.24461664</v>
+      </c>
+      <c r="N64">
+        <v>-8.00461664</v>
+      </c>
+      <c r="O64">
+        <v>-1.8410618272</v>
+      </c>
+      <c r="P64">
+        <v>-6.1635548128</v>
+      </c>
+      <c r="Q64">
+        <v>-6.0835548128</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.6108575233508327</v>
+      </c>
+      <c r="T64">
+        <v>3.339059079807704</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.03085038689067803</v>
+      </c>
+      <c r="W64">
+        <v>0.2314329276105061</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.1341321169159915</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.3776142739918302</v>
+      </c>
+      <c r="C65">
+        <v>1.988059474681656</v>
+      </c>
+      <c r="D65">
+        <v>40.52725947468166</v>
+      </c>
+      <c r="E65">
+        <v>35.0972</v>
+      </c>
+      <c r="F65">
+        <v>39.3372</v>
+      </c>
+      <c r="G65">
+        <v>0.798</v>
+      </c>
+      <c r="H65">
+        <v>58.2</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>1.32</v>
+      </c>
+      <c r="K65">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L65">
+        <v>1.24</v>
+      </c>
+      <c r="M65">
+        <v>9.393723360000001</v>
+      </c>
+      <c r="N65">
+        <v>-8.153723360000001</v>
+      </c>
+      <c r="O65">
+        <v>-1.8753563728</v>
+      </c>
+      <c r="P65">
+        <v>-6.278366987200001</v>
+      </c>
+      <c r="Q65">
+        <v>-6.198366987200001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.6263185374954499</v>
+      </c>
+      <c r="T65">
+        <v>3.429303919802507</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.03036069820987362</v>
+      </c>
+      <c r="W65">
+        <v>0.2315498652674822</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.1320030356951027</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.3796142739918302</v>
+      </c>
+      <c r="C66">
+        <v>1.12583340595512</v>
+      </c>
+      <c r="D66">
+        <v>40.28943340595512</v>
+      </c>
+      <c r="E66">
+        <v>35.7216</v>
+      </c>
+      <c r="F66">
+        <v>39.9616</v>
+      </c>
+      <c r="G66">
+        <v>0.798</v>
+      </c>
+      <c r="H66">
+        <v>58.2</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>1.32</v>
+      </c>
+      <c r="K66">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L66">
+        <v>1.24</v>
+      </c>
+      <c r="M66">
+        <v>9.542830080000002</v>
+      </c>
+      <c r="N66">
+        <v>-8.302830080000001</v>
+      </c>
+      <c r="O66">
+        <v>-1.9096509184</v>
+      </c>
+      <c r="P66">
+        <v>-6.393179161600001</v>
+      </c>
+      <c r="Q66">
+        <v>-6.313179161600001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.6426384968703234</v>
+      </c>
+      <c r="T66">
+        <v>3.524562362019243</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.02988631230034433</v>
+      </c>
+      <c r="W66">
+        <v>0.2316631486226778</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.1299404882623667</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.3816142739918302</v>
+      </c>
+      <c r="C67">
+        <v>0.2663823216649988</v>
+      </c>
+      <c r="D67">
+        <v>40.054382321665</v>
+      </c>
+      <c r="E67">
+        <v>36.346</v>
+      </c>
+      <c r="F67">
+        <v>40.58600000000001</v>
+      </c>
+      <c r="G67">
+        <v>0.798</v>
+      </c>
+      <c r="H67">
+        <v>58.2</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>1.32</v>
+      </c>
+      <c r="K67">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L67">
+        <v>1.24</v>
+      </c>
+      <c r="M67">
+        <v>9.691936800000002</v>
+      </c>
+      <c r="N67">
+        <v>-8.451936800000002</v>
+      </c>
+      <c r="O67">
+        <v>-1.943945464</v>
+      </c>
+      <c r="P67">
+        <v>-6.507991336000002</v>
+      </c>
+      <c r="Q67">
+        <v>-6.427991336000002</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.6598910253523327</v>
+      </c>
+      <c r="T67">
+        <v>3.625264143791222</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.02942652288033903</v>
+      </c>
+      <c r="W67">
+        <v>0.2317729463361751</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.127941403827561</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.3836142739918303</v>
+      </c>
+      <c r="C68">
+        <v>-0.5903420647820425</v>
+      </c>
+      <c r="D68">
+        <v>39.82205793521796</v>
+      </c>
+      <c r="E68">
+        <v>36.97040000000001</v>
+      </c>
+      <c r="F68">
+        <v>41.21040000000001</v>
+      </c>
+      <c r="G68">
+        <v>0.798</v>
+      </c>
+      <c r="H68">
+        <v>58.2</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>1.32</v>
+      </c>
+      <c r="K68">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L68">
+        <v>1.24</v>
+      </c>
+      <c r="M68">
+        <v>9.841043520000003</v>
+      </c>
+      <c r="N68">
+        <v>-8.601043520000003</v>
+      </c>
+      <c r="O68">
+        <v>-1.978240009600001</v>
+      </c>
+      <c r="P68">
+        <v>-6.622803510400002</v>
+      </c>
+      <c r="Q68">
+        <v>-6.542803510400002</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.6781584084509309</v>
+      </c>
+      <c r="T68">
+        <v>3.731889559785081</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.02898066647306117</v>
+      </c>
+      <c r="W68">
+        <v>0.231879416846233</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.1260028977089617</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.3856142739918302</v>
+      </c>
+      <c r="C69">
+        <v>-1.444386926147551</v>
+      </c>
+      <c r="D69">
+        <v>39.59241307385246</v>
+      </c>
+      <c r="E69">
+        <v>37.59480000000001</v>
+      </c>
+      <c r="F69">
+        <v>41.83480000000001</v>
+      </c>
+      <c r="G69">
+        <v>0.798</v>
+      </c>
+      <c r="H69">
+        <v>58.2</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>1.32</v>
+      </c>
+      <c r="K69">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L69">
+        <v>1.24</v>
+      </c>
+      <c r="M69">
+        <v>9.990150240000002</v>
+      </c>
+      <c r="N69">
+        <v>-8.750150240000002</v>
+      </c>
+      <c r="O69">
+        <v>-2.0125345552</v>
+      </c>
+      <c r="P69">
+        <v>-6.737615684800002</v>
+      </c>
+      <c r="Q69">
+        <v>-6.657615684800001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.6975329056767166</v>
+      </c>
+      <c r="T69">
+        <v>3.844977122202811</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.02854811921226922</v>
+      </c>
+      <c r="W69">
+        <v>0.2319827091321101</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.1241222574446488</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.3876142739918302</v>
+      </c>
+      <c r="C70">
+        <v>-2.295798353293335</v>
+      </c>
+      <c r="D70">
+        <v>39.36540164670667</v>
+      </c>
+      <c r="E70">
+        <v>38.21920000000001</v>
+      </c>
+      <c r="F70">
+        <v>42.45920000000001</v>
+      </c>
+      <c r="G70">
+        <v>0.798</v>
+      </c>
+      <c r="H70">
+        <v>58.2</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>1.32</v>
+      </c>
+      <c r="K70">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L70">
+        <v>1.24</v>
+      </c>
+      <c r="M70">
+        <v>10.13925696</v>
+      </c>
+      <c r="N70">
+        <v>-8.899256960000002</v>
+      </c>
+      <c r="O70">
+        <v>-2.046829100800001</v>
+      </c>
+      <c r="P70">
+        <v>-6.852427859200002</v>
+      </c>
+      <c r="Q70">
+        <v>-6.772427859200002</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.7181183089791139</v>
+      </c>
+      <c r="T70">
+        <v>3.965132657271649</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.02812829392973584</v>
+      </c>
+      <c r="W70">
+        <v>0.2320829634095791</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.1222969301292863</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.3896142739918302</v>
+      </c>
+      <c r="C71">
+        <v>-3.144621386021036</v>
+      </c>
+      <c r="D71">
+        <v>39.14097861397897</v>
+      </c>
+      <c r="E71">
+        <v>38.8436</v>
+      </c>
+      <c r="F71">
+        <v>43.0836</v>
+      </c>
+      <c r="G71">
+        <v>0.798</v>
+      </c>
+      <c r="H71">
+        <v>58.2</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>1.32</v>
+      </c>
+      <c r="K71">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L71">
+        <v>1.24</v>
+      </c>
+      <c r="M71">
+        <v>10.28836368</v>
+      </c>
+      <c r="N71">
+        <v>-9.048363680000001</v>
+      </c>
+      <c r="O71">
+        <v>-2.0811236464</v>
+      </c>
+      <c r="P71">
+        <v>-6.967240033600001</v>
+      </c>
+      <c r="Q71">
+        <v>-6.887240033600001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.74003180281715</v>
+      </c>
+      <c r="T71">
+        <v>4.093040162344928</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.02772063749597156</v>
+      </c>
+      <c r="W71">
+        <v>0.232180311765962</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1205245108520503</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.3916142739918302</v>
+      </c>
+      <c r="C72">
+        <v>-3.990900042862933</v>
+      </c>
+      <c r="D72">
+        <v>38.91909995713707</v>
+      </c>
+      <c r="E72">
+        <v>39.468</v>
+      </c>
+      <c r="F72">
+        <v>43.70800000000001</v>
+      </c>
+      <c r="G72">
+        <v>0.798</v>
+      </c>
+      <c r="H72">
+        <v>58.2</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>1.32</v>
+      </c>
+      <c r="K72">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L72">
+        <v>1.24</v>
+      </c>
+      <c r="M72">
+        <v>10.4374704</v>
+      </c>
+      <c r="N72">
+        <v>-9.197470400000002</v>
+      </c>
+      <c r="O72">
+        <v>-2.115418192</v>
+      </c>
+      <c r="P72">
+        <v>-7.082052208000002</v>
+      </c>
+      <c r="Q72">
+        <v>-7.002052208000002</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.7634061962443883</v>
+      </c>
+      <c r="T72">
+        <v>4.229474834423092</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.02732462838888625</v>
+      </c>
+      <c r="W72">
+        <v>0.232274878740734</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1188027321255924</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.3936142739918302</v>
+      </c>
+      <c r="C73">
+        <v>-4.834677349865146</v>
+      </c>
+      <c r="D73">
+        <v>38.69972265013485</v>
+      </c>
+      <c r="E73">
+        <v>40.0924</v>
+      </c>
+      <c r="F73">
+        <v>44.3324</v>
+      </c>
+      <c r="G73">
+        <v>0.798</v>
+      </c>
+      <c r="H73">
+        <v>58.2</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>1.32</v>
+      </c>
+      <c r="K73">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L73">
+        <v>1.24</v>
+      </c>
+      <c r="M73">
+        <v>10.58657712</v>
+      </c>
+      <c r="N73">
+        <v>-9.346577120000001</v>
+      </c>
+      <c r="O73">
+        <v>-2.1497127376</v>
+      </c>
+      <c r="P73">
+        <v>-7.196864382400001</v>
+      </c>
+      <c r="Q73">
+        <v>-7.116864382400001</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.7883926168045394</v>
+      </c>
+      <c r="T73">
+        <v>4.375318794230783</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.02693977446791602</v>
+      </c>
+      <c r="W73">
+        <v>0.2323667818570617</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1171294542083305</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.3956142739918302</v>
+      </c>
+      <c r="C74">
+        <v>-5.67599536840283</v>
+      </c>
+      <c r="D74">
+        <v>38.48280463159717</v>
+      </c>
+      <c r="E74">
+        <v>40.7168</v>
+      </c>
+      <c r="F74">
+        <v>44.9568</v>
+      </c>
+      <c r="G74">
+        <v>0.798</v>
+      </c>
+      <c r="H74">
+        <v>58.2</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>1.32</v>
+      </c>
+      <c r="K74">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L74">
+        <v>1.24</v>
+      </c>
+      <c r="M74">
+        <v>10.73568384</v>
+      </c>
+      <c r="N74">
+        <v>-9.49568384</v>
+      </c>
+      <c r="O74">
+        <v>-2.1840072832</v>
+      </c>
+      <c r="P74">
+        <v>-7.3116765568</v>
+      </c>
+      <c r="Q74">
+        <v>-7.2316765568</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.8151637816904158</v>
+      </c>
+      <c r="T74">
+        <v>4.531580179739026</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.02656561093363942</v>
+      </c>
+      <c r="W74">
+        <v>0.2324561321090469</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1155026562332149</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.3976142739918301</v>
+      </c>
+      <c r="C75">
+        <v>-6.514895222065128</v>
+      </c>
+      <c r="D75">
+        <v>38.26830477793487</v>
+      </c>
+      <c r="E75">
+        <v>41.3412</v>
+      </c>
+      <c r="F75">
+        <v>45.5812</v>
+      </c>
+      <c r="G75">
+        <v>0.798</v>
+      </c>
+      <c r="H75">
+        <v>58.2</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>1.32</v>
+      </c>
+      <c r="K75">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L75">
+        <v>1.24</v>
+      </c>
+      <c r="M75">
+        <v>10.88479056</v>
+      </c>
+      <c r="N75">
+        <v>-9.644790560000001</v>
+      </c>
+      <c r="O75">
+        <v>-2.2183018288</v>
+      </c>
+      <c r="P75">
+        <v>-7.426488731200001</v>
+      </c>
+      <c r="Q75">
+        <v>-7.346488731200001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.8439179958270977</v>
+      </c>
+      <c r="T75">
+        <v>4.699416482692323</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.02620169845509641</v>
+      </c>
+      <c r="W75">
+        <v>0.232543034408923</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.1139204280656366</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.3996142739918302</v>
+      </c>
+      <c r="C76">
+        <v>-7.351417122646055</v>
+      </c>
+      <c r="D76">
+        <v>38.05618287735395</v>
+      </c>
+      <c r="E76">
+        <v>41.9656</v>
+      </c>
+      <c r="F76">
+        <v>46.2056</v>
+      </c>
+      <c r="G76">
+        <v>0.798</v>
+      </c>
+      <c r="H76">
+        <v>58.2</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>1.32</v>
+      </c>
+      <c r="K76">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L76">
+        <v>1.24</v>
+      </c>
+      <c r="M76">
+        <v>11.03389728</v>
+      </c>
+      <c r="N76">
+        <v>-9.793897280000001</v>
+      </c>
+      <c r="O76">
+        <v>-2.2525963744</v>
+      </c>
+      <c r="P76">
+        <v>-7.541300905600002</v>
+      </c>
+      <c r="Q76">
+        <v>-7.461300905600002</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.8748840725896787</v>
+      </c>
+      <c r="T76">
+        <v>4.880163270488183</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.02584762144894645</v>
+      </c>
+      <c r="W76">
+        <v>0.2326275879979916</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1123809628215063</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.4016142739918303</v>
+      </c>
+      <c r="C77">
+        <v>-8.185600395275571</v>
+      </c>
+      <c r="D77">
+        <v>37.84639960472443</v>
+      </c>
+      <c r="E77">
+        <v>42.59</v>
+      </c>
+      <c r="F77">
+        <v>46.83000000000001</v>
+      </c>
+      <c r="G77">
+        <v>0.798</v>
+      </c>
+      <c r="H77">
+        <v>58.2</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>1.32</v>
+      </c>
+      <c r="K77">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L77">
+        <v>1.24</v>
+      </c>
+      <c r="M77">
+        <v>11.183004</v>
+      </c>
+      <c r="N77">
+        <v>-9.943004000000002</v>
+      </c>
+      <c r="O77">
+        <v>-2.28689092</v>
+      </c>
+      <c r="P77">
+        <v>-7.656113080000002</v>
+      </c>
+      <c r="Q77">
+        <v>-7.576113080000002</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.9083274354932658</v>
+      </c>
+      <c r="T77">
+        <v>5.07536980130771</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.02550298649629383</v>
+      </c>
+      <c r="W77">
+        <v>0.232709886824685</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1108825499838862</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.4036142739918303</v>
+      </c>
+      <c r="C78">
+        <v>-9.017483502724225</v>
+      </c>
+      <c r="D78">
+        <v>37.63891649727578</v>
+      </c>
+      <c r="E78">
+        <v>43.2144</v>
+      </c>
+      <c r="F78">
+        <v>47.45440000000001</v>
+      </c>
+      <c r="G78">
+        <v>0.798</v>
+      </c>
+      <c r="H78">
+        <v>58.2</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>1.32</v>
+      </c>
+      <c r="K78">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L78">
+        <v>1.24</v>
+      </c>
+      <c r="M78">
+        <v>11.33211072</v>
+      </c>
+      <c r="N78">
+        <v>-10.09211072</v>
+      </c>
+      <c r="O78">
+        <v>-2.321185465600001</v>
+      </c>
+      <c r="P78">
+        <v>-7.770925254400002</v>
+      </c>
+      <c r="Q78">
+        <v>-7.690925254400002</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.9445577453054852</v>
+      </c>
+      <c r="T78">
+        <v>5.286843543028865</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.02516742088450049</v>
+      </c>
+      <c r="W78">
+        <v>0.2327900198927813</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.1094235690630456</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.4056142739918303</v>
+      </c>
+      <c r="C79">
+        <v>-9.847104068912522</v>
+      </c>
+      <c r="D79">
+        <v>37.43369593108748</v>
+      </c>
+      <c r="E79">
+        <v>43.83880000000001</v>
+      </c>
+      <c r="F79">
+        <v>48.07880000000001</v>
+      </c>
+      <c r="G79">
+        <v>0.798</v>
+      </c>
+      <c r="H79">
+        <v>58.2</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1.32</v>
+      </c>
+      <c r="K79">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L79">
+        <v>1.24</v>
+      </c>
+      <c r="M79">
+        <v>11.48121744</v>
+      </c>
+      <c r="N79">
+        <v>-10.24121744</v>
+      </c>
+      <c r="O79">
+        <v>-2.3554800112</v>
+      </c>
+      <c r="P79">
+        <v>-7.885737428800002</v>
+      </c>
+      <c r="Q79">
+        <v>-7.805737428800001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.9839385168405064</v>
+      </c>
+      <c r="T79">
+        <v>5.51670630576925</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.02484057126262386</v>
+      </c>
+      <c r="W79">
+        <v>0.2328680715824854</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1080024837505386</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.4076142739918303</v>
+      </c>
+      <c r="C80">
+        <v>-10.67449890165544</v>
+      </c>
+      <c r="D80">
+        <v>37.23070109834456</v>
+      </c>
+      <c r="E80">
+        <v>44.4632</v>
+      </c>
+      <c r="F80">
+        <v>48.7032</v>
+      </c>
+      <c r="G80">
+        <v>0.798</v>
+      </c>
+      <c r="H80">
+        <v>58.2</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>1.32</v>
+      </c>
+      <c r="K80">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L80">
+        <v>1.24</v>
+      </c>
+      <c r="M80">
+        <v>11.63032416</v>
+      </c>
+      <c r="N80">
+        <v>-10.39032416</v>
+      </c>
+      <c r="O80">
+        <v>-2.3897745568</v>
+      </c>
+      <c r="P80">
+        <v>-8.0005496032</v>
+      </c>
+      <c r="Q80">
+        <v>-7.9205496032</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>1.026899358515075</v>
+      </c>
+      <c r="T80">
+        <v>5.767465683304216</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.02452210240028253</v>
+      </c>
+      <c r="W80">
+        <v>0.2329441219468125</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1066178365229675</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.4096142739918302</v>
+      </c>
+      <c r="C81">
+        <v>-11.49970401467094</v>
+      </c>
+      <c r="D81">
+        <v>37.02989598532906</v>
+      </c>
+      <c r="E81">
+        <v>45.0876</v>
+      </c>
+      <c r="F81">
+        <v>49.3276</v>
+      </c>
+      <c r="G81">
+        <v>0.798</v>
+      </c>
+      <c r="H81">
+        <v>58.2</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>1.32</v>
+      </c>
+      <c r="K81">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L81">
+        <v>1.24</v>
+      </c>
+      <c r="M81">
+        <v>11.77943088</v>
+      </c>
+      <c r="N81">
+        <v>-10.53943088</v>
+      </c>
+      <c r="O81">
+        <v>-2.4240691024</v>
+      </c>
+      <c r="P81">
+        <v>-8.1153617776</v>
+      </c>
+      <c r="Q81">
+        <v>-8.0353617776</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>1.073951708920555</v>
+      </c>
+      <c r="T81">
+        <v>6.042106906318702</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.02421169604078529</v>
+      </c>
+      <c r="W81">
+        <v>0.2330182469854605</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1052682436555882</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.4116142739918303</v>
+      </c>
+      <c r="C82">
+        <v>-12.32275464887997</v>
+      </c>
+      <c r="D82">
+        <v>36.83124535112003</v>
+      </c>
+      <c r="E82">
+        <v>45.712</v>
+      </c>
+      <c r="F82">
+        <v>49.95200000000001</v>
+      </c>
+      <c r="G82">
+        <v>0.798</v>
+      </c>
+      <c r="H82">
+        <v>58.2</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>1.32</v>
+      </c>
+      <c r="K82">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L82">
+        <v>1.24</v>
+      </c>
+      <c r="M82">
+        <v>11.9285376</v>
+      </c>
+      <c r="N82">
+        <v>-10.6885376</v>
+      </c>
+      <c r="O82">
+        <v>-2.458363648</v>
+      </c>
+      <c r="P82">
+        <v>-8.230173952000001</v>
+      </c>
+      <c r="Q82">
+        <v>-8.150173952000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>1.125709294366582</v>
+      </c>
+      <c r="T82">
+        <v>6.344212251634638</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.02390904984027547</v>
+      </c>
+      <c r="W82">
+        <v>0.2330905188981423</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1039523906098934</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.4136142739918303</v>
+      </c>
+      <c r="C83">
+        <v>-13.14368529302467</v>
+      </c>
+      <c r="D83">
+        <v>36.63471470697533</v>
+      </c>
+      <c r="E83">
+        <v>46.3364</v>
+      </c>
+      <c r="F83">
+        <v>50.57640000000001</v>
+      </c>
+      <c r="G83">
+        <v>0.798</v>
+      </c>
+      <c r="H83">
+        <v>58.2</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>1.32</v>
+      </c>
+      <c r="K83">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L83">
+        <v>1.24</v>
+      </c>
+      <c r="M83">
+        <v>12.07764432</v>
+      </c>
+      <c r="N83">
+        <v>-10.83764432</v>
+      </c>
+      <c r="O83">
+        <v>-2.492658193600001</v>
+      </c>
+      <c r="P83">
+        <v>-8.344986126400002</v>
+      </c>
+      <c r="Q83">
+        <v>-8.264986126400002</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>1.182915046701666</v>
+      </c>
+      <c r="T83">
+        <v>6.678118159615409</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.02361387638545725</v>
+      </c>
+      <c r="W83">
+        <v>0.2331610063191528</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1026690277628577</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.4156142739918303</v>
+      </c>
+      <c r="C84">
+        <v>-13.96252970362983</v>
+      </c>
+      <c r="D84">
+        <v>36.44027029637018</v>
+      </c>
+      <c r="E84">
+        <v>46.96080000000001</v>
+      </c>
+      <c r="F84">
+        <v>51.20080000000001</v>
+      </c>
+      <c r="G84">
+        <v>0.798</v>
+      </c>
+      <c r="H84">
+        <v>58.2</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>1.32</v>
+      </c>
+      <c r="K84">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L84">
+        <v>1.24</v>
+      </c>
+      <c r="M84">
+        <v>12.22675104</v>
+      </c>
+      <c r="N84">
+        <v>-10.98675104</v>
+      </c>
+      <c r="O84">
+        <v>-2.5269527392</v>
+      </c>
+      <c r="P84">
+        <v>-8.459798300800001</v>
+      </c>
+      <c r="Q84">
+        <v>-8.379798300800001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>1.246476993740647</v>
+      </c>
+      <c r="T84">
+        <v>7.049124724038488</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.02332590228319558</v>
+      </c>
+      <c r="W84">
+        <v>0.2332297745347729</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1014169664486765</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.4176142739918303</v>
+      </c>
+      <c r="C85">
+        <v>-14.77932092433212</v>
+      </c>
+      <c r="D85">
+        <v>36.24787907566789</v>
+      </c>
+      <c r="E85">
+        <v>47.58520000000001</v>
+      </c>
+      <c r="F85">
+        <v>51.82520000000001</v>
+      </c>
+      <c r="G85">
+        <v>0.798</v>
+      </c>
+      <c r="H85">
+        <v>58.2</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>1.32</v>
+      </c>
+      <c r="K85">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L85">
+        <v>1.24</v>
+      </c>
+      <c r="M85">
+        <v>12.37585776</v>
+      </c>
+      <c r="N85">
+        <v>-11.13585776</v>
+      </c>
+      <c r="O85">
+        <v>-2.5612472848</v>
+      </c>
+      <c r="P85">
+        <v>-8.574610475200002</v>
+      </c>
+      <c r="Q85">
+        <v>-8.494610475200002</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>1.317516816901862</v>
+      </c>
+      <c r="T85">
+        <v>7.463779119570164</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.02304486731592816</v>
+      </c>
+      <c r="W85">
+        <v>0.2332968856849564</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1001950752866442</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.4196142739918302</v>
+      </c>
+      <c r="C86">
+        <v>-15.59409130460018</v>
+      </c>
+      <c r="D86">
+        <v>36.05750869539982</v>
+      </c>
+      <c r="E86">
+        <v>48.2096</v>
+      </c>
+      <c r="F86">
+        <v>52.4496</v>
+      </c>
+      <c r="G86">
+        <v>0.798</v>
+      </c>
+      <c r="H86">
+        <v>58.2</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>1.32</v>
+      </c>
+      <c r="K86">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L86">
+        <v>1.24</v>
+      </c>
+      <c r="M86">
+        <v>12.52496448</v>
+      </c>
+      <c r="N86">
+        <v>-11.28496448</v>
+      </c>
+      <c r="O86">
+        <v>-2.5955418304</v>
+      </c>
+      <c r="P86">
+        <v>-8.689422649600001</v>
+      </c>
+      <c r="Q86">
+        <v>-8.609422649600001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>1.397436617958228</v>
+      </c>
+      <c r="T86">
+        <v>7.930265314543296</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.02277052365740521</v>
+      </c>
+      <c r="W86">
+        <v>0.2333623989506116</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.099002276771327</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.4216142739918303</v>
+      </c>
+      <c r="C87">
+        <v>-16.40687251786795</v>
+      </c>
+      <c r="D87">
+        <v>35.86912748213205</v>
+      </c>
+      <c r="E87">
+        <v>48.834</v>
+      </c>
+      <c r="F87">
+        <v>53.07400000000001</v>
+      </c>
+      <c r="G87">
+        <v>0.798</v>
+      </c>
+      <c r="H87">
+        <v>58.2</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>1.32</v>
+      </c>
+      <c r="K87">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L87">
+        <v>1.24</v>
+      </c>
+      <c r="M87">
+        <v>12.6740712</v>
+      </c>
+      <c r="N87">
+        <v>-11.4340712</v>
+      </c>
+      <c r="O87">
+        <v>-2.629836376</v>
+      </c>
+      <c r="P87">
+        <v>-8.804234824000002</v>
+      </c>
+      <c r="Q87">
+        <v>-8.724234824000002</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>1.488012392488776</v>
+      </c>
+      <c r="T87">
+        <v>8.458949668846182</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.02250263514378868</v>
+      </c>
+      <c r="W87">
+        <v>0.2334263707276633</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.09783754410342904</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.4236142739918303</v>
+      </c>
+      <c r="C88">
+        <v>-17.2176955791024</v>
+      </c>
+      <c r="D88">
+        <v>35.68270442089761</v>
+      </c>
+      <c r="E88">
+        <v>49.4584</v>
+      </c>
+      <c r="F88">
+        <v>53.69840000000001</v>
+      </c>
+      <c r="G88">
+        <v>0.798</v>
+      </c>
+      <c r="H88">
+        <v>58.2</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>1.32</v>
+      </c>
+      <c r="K88">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L88">
+        <v>1.24</v>
+      </c>
+      <c r="M88">
+        <v>12.82317792</v>
+      </c>
+      <c r="N88">
+        <v>-11.58317792</v>
+      </c>
+      <c r="O88">
+        <v>-2.6641309216</v>
+      </c>
+      <c r="P88">
+        <v>-8.919046998400002</v>
+      </c>
+      <c r="Q88">
+        <v>-8.839046998400002</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>1.591527563380832</v>
+      </c>
+      <c r="T88">
+        <v>9.063160359478053</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.02224097659560509</v>
+      </c>
+      <c r="W88">
+        <v>0.2334888547889695</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.09669989824176128</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.4256142739918302</v>
+      </c>
+      <c r="C89">
+        <v>-18.02659086182637</v>
+      </c>
+      <c r="D89">
+        <v>35.49820913817363</v>
+      </c>
+      <c r="E89">
+        <v>50.0828</v>
+      </c>
+      <c r="F89">
+        <v>54.3228</v>
+      </c>
+      <c r="G89">
+        <v>0.798</v>
+      </c>
+      <c r="H89">
+        <v>58.2</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>1.32</v>
+      </c>
+      <c r="K89">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L89">
+        <v>1.24</v>
+      </c>
+      <c r="M89">
+        <v>12.97228464</v>
+      </c>
+      <c r="N89">
+        <v>-11.73228464</v>
+      </c>
+      <c r="O89">
+        <v>-2.6984254672</v>
+      </c>
+      <c r="P89">
+        <v>-9.033859172800002</v>
+      </c>
+      <c r="Q89">
+        <v>-8.953859172800001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>1.710968145179357</v>
+      </c>
+      <c r="T89">
+        <v>9.760326540976363</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.0219853331864602</v>
+      </c>
+      <c r="W89">
+        <v>0.2335499024350733</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.09558840515852263</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.4276142739918303</v>
+      </c>
+      <c r="C90">
+        <v>-18.83358811461612</v>
+      </c>
+      <c r="D90">
+        <v>35.31561188538388</v>
+      </c>
+      <c r="E90">
+        <v>50.7072</v>
+      </c>
+      <c r="F90">
+        <v>54.9472</v>
+      </c>
+      <c r="G90">
+        <v>0.798</v>
+      </c>
+      <c r="H90">
+        <v>58.2</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>1.32</v>
+      </c>
+      <c r="K90">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L90">
+        <v>1.24</v>
+      </c>
+      <c r="M90">
+        <v>13.12139136</v>
+      </c>
+      <c r="N90">
+        <v>-11.88139136</v>
+      </c>
+      <c r="O90">
+        <v>-2.7327200128</v>
+      </c>
+      <c r="P90">
+        <v>-9.148671347200001</v>
+      </c>
+      <c r="Q90">
+        <v>-9.0686713472</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>1.85031549061097</v>
+      </c>
+      <c r="T90">
+        <v>10.57368708605773</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.02173549985479588</v>
+      </c>
+      <c r="W90">
+        <v>0.2336095626346748</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.09450217328172128</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.4296142739918302</v>
+      </c>
+      <c r="C91">
+        <v>-19.63871647709205</v>
+      </c>
+      <c r="D91">
+        <v>35.13488352290795</v>
+      </c>
+      <c r="E91">
+        <v>51.3316</v>
+      </c>
+      <c r="F91">
+        <v>55.5716</v>
+      </c>
+      <c r="G91">
+        <v>0.798</v>
+      </c>
+      <c r="H91">
+        <v>58.2</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1.32</v>
+      </c>
+      <c r="K91">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L91">
+        <v>1.24</v>
+      </c>
+      <c r="M91">
+        <v>13.27049808</v>
+      </c>
+      <c r="N91">
+        <v>-12.03049808</v>
+      </c>
+      <c r="O91">
+        <v>-2.7670145584</v>
+      </c>
+      <c r="P91">
+        <v>-9.263483521600001</v>
+      </c>
+      <c r="Q91">
+        <v>-9.183483521600001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>2.014998717030149</v>
+      </c>
+      <c r="T91">
+        <v>11.53493136660843</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.02149128075530379</v>
+      </c>
+      <c r="W91">
+        <v>0.2336678821556335</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.09344035111001647</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.4316142739918302</v>
+      </c>
+      <c r="C92">
+        <v>-20.44200449542124</v>
+      </c>
+      <c r="D92">
+        <v>34.95599550457877</v>
+      </c>
+      <c r="E92">
+        <v>51.956</v>
+      </c>
+      <c r="F92">
+        <v>56.19600000000001</v>
+      </c>
+      <c r="G92">
+        <v>0.798</v>
+      </c>
+      <c r="H92">
+        <v>58.2</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1.32</v>
+      </c>
+      <c r="K92">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L92">
+        <v>1.24</v>
+      </c>
+      <c r="M92">
+        <v>13.4196048</v>
+      </c>
+      <c r="N92">
+        <v>-12.1796048</v>
+      </c>
+      <c r="O92">
+        <v>-2.801309104</v>
+      </c>
+      <c r="P92">
+        <v>-9.378295696000002</v>
+      </c>
+      <c r="Q92">
+        <v>-9.298295696000002</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>2.212618588733165</v>
+      </c>
+      <c r="T92">
+        <v>12.68842450326928</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.02125248874691153</v>
+      </c>
+      <c r="W92">
+        <v>0.2337249056872375</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.09240212498657185</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.4336142739918302</v>
+      </c>
+      <c r="C93">
+        <v>-21.24348013734853</v>
+      </c>
+      <c r="D93">
+        <v>34.77891986265148</v>
+      </c>
+      <c r="E93">
+        <v>52.5804</v>
+      </c>
+      <c r="F93">
+        <v>56.82040000000001</v>
+      </c>
+      <c r="G93">
+        <v>0.798</v>
+      </c>
+      <c r="H93">
+        <v>58.2</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>1.32</v>
+      </c>
+      <c r="K93">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L93">
+        <v>1.24</v>
+      </c>
+      <c r="M93">
+        <v>13.56871152</v>
+      </c>
+      <c r="N93">
+        <v>-12.32871152</v>
+      </c>
+      <c r="O93">
+        <v>-2.8356036496</v>
+      </c>
+      <c r="P93">
+        <v>-9.493107870400003</v>
+      </c>
+      <c r="Q93">
+        <v>-9.413107870400003</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>2.454153987481295</v>
+      </c>
+      <c r="T93">
+        <v>14.09824944807698</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.02101894491452789</v>
+      </c>
+      <c r="W93">
+        <v>0.2337806759544107</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.09138671701968648</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.4356142739918303</v>
+      </c>
+      <c r="C94">
+        <v>-22.04317080677323</v>
+      </c>
+      <c r="D94">
+        <v>34.60362919322677</v>
+      </c>
+      <c r="E94">
+        <v>53.20480000000001</v>
+      </c>
+      <c r="F94">
+        <v>57.44480000000001</v>
+      </c>
+      <c r="G94">
+        <v>0.798</v>
+      </c>
+      <c r="H94">
+        <v>58.2</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>1.32</v>
+      </c>
+      <c r="K94">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L94">
+        <v>1.24</v>
+      </c>
+      <c r="M94">
+        <v>13.71781824</v>
+      </c>
+      <c r="N94">
+        <v>-12.47781824</v>
+      </c>
+      <c r="O94">
+        <v>-2.869898195200001</v>
+      </c>
+      <c r="P94">
+        <v>-9.607920044800002</v>
+      </c>
+      <c r="Q94">
+        <v>-9.527920044800002</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>2.756073235916457</v>
+      </c>
+      <c r="T94">
+        <v>15.8605306290866</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.02079047812197867</v>
+      </c>
+      <c r="W94">
+        <v>0.2338352338244715</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.09039338313903766</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.4376142739918303</v>
+      </c>
+      <c r="C95">
+        <v>-22.84110335788717</v>
+      </c>
+      <c r="D95">
+        <v>34.43009664211284</v>
+      </c>
+      <c r="E95">
+        <v>53.82920000000001</v>
+      </c>
+      <c r="F95">
+        <v>58.06920000000001</v>
+      </c>
+      <c r="G95">
+        <v>0.798</v>
+      </c>
+      <c r="H95">
+        <v>58.2</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>1.32</v>
+      </c>
+      <c r="K95">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L95">
+        <v>1.24</v>
+      </c>
+      <c r="M95">
+        <v>13.86692496</v>
+      </c>
+      <c r="N95">
+        <v>-12.62692496</v>
+      </c>
+      <c r="O95">
+        <v>-2.9041927408</v>
+      </c>
+      <c r="P95">
+        <v>-9.722732219200001</v>
+      </c>
+      <c r="Q95">
+        <v>-9.642732219200001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>3.144255126761666</v>
+      </c>
+      <c r="T95">
+        <v>18.12632071895612</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.02056692459378535</v>
+      </c>
+      <c r="W95">
+        <v>0.2338886184070041</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.08942141127732761</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.4396142739918303</v>
+      </c>
+      <c r="C96">
+        <v>-23.63730410888943</v>
+      </c>
+      <c r="D96">
+        <v>34.25829589111058</v>
+      </c>
+      <c r="E96">
+        <v>54.45360000000001</v>
+      </c>
+      <c r="F96">
+        <v>58.69360000000001</v>
+      </c>
+      <c r="G96">
+        <v>0.798</v>
+      </c>
+      <c r="H96">
+        <v>58.2</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>1.32</v>
+      </c>
+      <c r="K96">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L96">
+        <v>1.24</v>
+      </c>
+      <c r="M96">
+        <v>14.01603168</v>
+      </c>
+      <c r="N96">
+        <v>-12.77603168</v>
+      </c>
+      <c r="O96">
+        <v>-2.9384872864</v>
+      </c>
+      <c r="P96">
+        <v>-9.837544393600002</v>
+      </c>
+      <c r="Q96">
+        <v>-9.757544393600002</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>3.661830981221944</v>
+      </c>
+      <c r="T96">
+        <v>21.14737417211548</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.0203481275236387</v>
+      </c>
+      <c r="W96">
+        <v>0.2339408671473551</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.08847011966799434</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.4416142739918303</v>
+      </c>
+      <c r="C97">
+        <v>-24.43179885529262</v>
+      </c>
+      <c r="D97">
+        <v>34.08820114470739</v>
+      </c>
+      <c r="E97">
+        <v>55.07800000000001</v>
+      </c>
+      <c r="F97">
+        <v>59.31800000000001</v>
+      </c>
+      <c r="G97">
+        <v>0.798</v>
+      </c>
+      <c r="H97">
+        <v>58.2</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>1.32</v>
+      </c>
+      <c r="K97">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L97">
+        <v>1.24</v>
+      </c>
+      <c r="M97">
+        <v>14.1651384</v>
+      </c>
+      <c r="N97">
+        <v>-12.9251384</v>
+      </c>
+      <c r="O97">
+        <v>-2.972781832</v>
+      </c>
+      <c r="P97">
+        <v>-9.952356568000003</v>
+      </c>
+      <c r="Q97">
+        <v>-9.872356568000002</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>4.386437177466335</v>
+      </c>
+      <c r="T97">
+        <v>25.37684900653858</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.02013393670760039</v>
+      </c>
+      <c r="W97">
+        <v>0.233992015914225</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.08753885525043648</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.4436142739918302</v>
+      </c>
+      <c r="C98">
+        <v>-25.2246128828345</v>
+      </c>
+      <c r="D98">
+        <v>33.9197871171655</v>
+      </c>
+      <c r="E98">
+        <v>55.7024</v>
+      </c>
+      <c r="F98">
+        <v>59.9424</v>
+      </c>
+      <c r="G98">
+        <v>0.798</v>
+      </c>
+      <c r="H98">
+        <v>58.2</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>1.32</v>
+      </c>
+      <c r="K98">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L98">
+        <v>1.24</v>
+      </c>
+      <c r="M98">
+        <v>14.31424512</v>
+      </c>
+      <c r="N98">
+        <v>-13.07424512</v>
+      </c>
+      <c r="O98">
+        <v>-3.0070763776</v>
+      </c>
+      <c r="P98">
+        <v>-10.0671687424</v>
+      </c>
+      <c r="Q98">
+        <v>-9.9871687424</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>5.473346471832906</v>
+      </c>
+      <c r="T98">
+        <v>31.72106125817316</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.01992420820022956</v>
+      </c>
+      <c r="W98">
+        <v>0.2340420990817852</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.0866269921749111</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.4456142739918303</v>
+      </c>
+      <c r="C99">
+        <v>-26.01577098000907</v>
+      </c>
+      <c r="D99">
+        <v>33.75302901999093</v>
+      </c>
+      <c r="E99">
+        <v>56.3268</v>
+      </c>
+      <c r="F99">
+        <v>60.5668</v>
+      </c>
+      <c r="G99">
+        <v>0.798</v>
+      </c>
+      <c r="H99">
+        <v>58.2</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>1.32</v>
+      </c>
+      <c r="K99">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L99">
+        <v>1.24</v>
+      </c>
+      <c r="M99">
+        <v>14.46335184</v>
+      </c>
+      <c r="N99">
+        <v>-13.22335184</v>
+      </c>
+      <c r="O99">
+        <v>-3.0413709232</v>
+      </c>
+      <c r="P99">
+        <v>-10.1819809168</v>
+      </c>
+      <c r="Q99">
+        <v>-10.1019809168</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>7.284861962443876</v>
+      </c>
+      <c r="T99">
+        <v>42.29474834423088</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.01971880399197977</v>
+      </c>
+      <c r="W99">
+        <v>0.2340911496067152</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.08573393039991206</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.4476142739918302</v>
+      </c>
+      <c r="C100">
+        <v>-26.80529745022945</v>
+      </c>
+      <c r="D100">
+        <v>33.58790254977055</v>
+      </c>
+      <c r="E100">
+        <v>56.9512</v>
+      </c>
+      <c r="F100">
+        <v>61.1912</v>
+      </c>
+      <c r="G100">
+        <v>0.798</v>
+      </c>
+      <c r="H100">
+        <v>58.2</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>1.32</v>
+      </c>
+      <c r="K100">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L100">
+        <v>1.24</v>
+      </c>
+      <c r="M100">
+        <v>14.61245856</v>
+      </c>
+      <c r="N100">
+        <v>-13.37245856</v>
+      </c>
+      <c r="O100">
+        <v>-3.0756654688</v>
+      </c>
+      <c r="P100">
+        <v>-10.2967930912</v>
+      </c>
+      <c r="Q100">
+        <v>-10.2167930912</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>10.90789294366581</v>
+      </c>
+      <c r="T100">
+        <v>63.44212251634632</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.01951759170634732</v>
+      </c>
+      <c r="W100">
+        <v>0.2341391991005242</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.08485909437542316</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.4496142739918302</v>
+      </c>
+      <c r="C101">
+        <v>-27.59321612363582</v>
+      </c>
+      <c r="D101">
+        <v>33.42438387636418</v>
+      </c>
+      <c r="E101">
+        <v>57.5756</v>
+      </c>
+      <c r="F101">
+        <v>61.8156</v>
+      </c>
+      <c r="G101">
+        <v>0.798</v>
+      </c>
+      <c r="H101">
+        <v>58.2</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>1.32</v>
+      </c>
+      <c r="K101">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="L101">
+        <v>1.24</v>
+      </c>
+      <c r="M101">
+        <v>14.76156528</v>
+      </c>
+      <c r="N101">
+        <v>-13.52156528</v>
+      </c>
+      <c r="O101">
+        <v>-3.1099600144</v>
+      </c>
+      <c r="P101">
+        <v>-10.4116052656</v>
+      </c>
+      <c r="Q101">
+        <v>-10.3316052656</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>21.77698588733162</v>
+      </c>
+      <c r="T101">
+        <v>126.8842450326926</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.01932044431537412</v>
+      </c>
+      <c r="W101">
+        <v>0.2341862778974887</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.08400193180597448</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
